--- a/docs/詳細設計書/詳細設計書_認証.xlsx
+++ b/docs/詳細設計書/詳細設計書_認証.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="14055"/>
+    <workbookView windowWidth="19815" windowHeight="7575"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="11" r:id="rId1"/>
@@ -16,15 +16,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">機能概要!$A$1:$AO$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">画面イメージ!$A$1:$AL$108</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">画面項目仕様!$A$1:$N$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">画面イメージ!$A$1:$AL$79</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">画面項目仕様!$A$1:$N$17</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="131">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -56,7 +56,7 @@
     <t>◆画面項目仕様　新規作成
 ◆画面イメージ　新規作成
 ◆処理詳細　修正
-・入力、出力、ログ処理の記載</t>
+　・入力、出力、ログ処理の記載</t>
   </si>
   <si>
     <t>機能概要</t>
@@ -182,7 +182,7 @@
     <t>ラベル</t>
   </si>
   <si>
-    <t xml:space="preserve">  adminId</t>
+    <t>adminId</t>
   </si>
   <si>
     <t>テキストボックス</t>
@@ -191,19 +191,17 @@
     <t>検索用のテキスト入力が可能</t>
   </si>
   <si>
-    <t>入力エラー：入力チェックに該当するの文字</t>
+    <t>入力エラー：入力チェックに該当する文字
+(入力チェックに該当する文字は処理詳細照)</t>
   </si>
   <si>
-    <t>入力時: 不正文字を入力したら表示</t>
+    <t>フォーカス遷移時に不正文字チェックを実行する。</t>
   </si>
   <si>
-    <t xml:space="preserve">  password</t>
+    <t>password</t>
   </si>
   <si>
-    <t>入力時：値をハッシュ化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  LOGIN</t>
+    <t>LOGIN</t>
   </si>
   <si>
     <t>ボタン</t>
@@ -212,7 +210,7 @@
     <t>認証情報を送信するボタン</t>
   </si>
   <si>
-    <t>クリック時: 在庫管理一覧を表示</t>
+    <t>押下時：パスワードをハッシュ化し、在庫管理一覧を表示する。</t>
   </si>
   <si>
     <t>画面イメージ</t>
@@ -222,15 +220,6 @@
   </si>
   <si>
     <t>初期表示で、認証画面を以下の通り出力する。</t>
-  </si>
-  <si>
-    <t>adminId</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>LOGIN</t>
   </si>
   <si>
     <r>
@@ -259,10 +248,10 @@
     <t>検索項目に何も入力されない状態で「LOGIN」ボタンが押下された場合、エラーメッセージを出力する。</t>
   </si>
   <si>
-    <t>ログインIDまたはパスワードが不正です。</t>
+    <t>検索項目「admin」または「password」に不正な文字列が入力された状態で「LOGIN」ボタンが押下された場合、エラーメッセージを出力する。</t>
   </si>
   <si>
-    <t>検索項目「admin」または「password」に不正な文字列が入力された状態で「LOGIN」ボタンが押下された場合、エラーメッセージを出力する。</t>
+    <t>ログインIDまたはパスワードが不正です。</t>
   </si>
   <si>
     <t>処理詳細</t>
@@ -492,8 +481,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="45">
     <font>
@@ -641,16 +630,16 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
       <name val="游ゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -663,43 +652,41 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -717,15 +704,56 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -739,56 +767,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -837,7 +826,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -849,7 +862,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -861,37 +976,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -909,108 +994,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="30">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1192,6 +1181,19 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1250,8 +1252,23 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom style="dotted">
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1261,11 +1278,51 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="dotted">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="dotted">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1286,21 +1343,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -1311,26 +1353,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1352,18 +1374,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1375,7 +1390,7 @@
     <xf numFmtId="43" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="16" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1384,7 +1399,7 @@
     <xf numFmtId="178" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1393,134 +1408,134 @@
     <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="15" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2037,50 +2052,56 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6988,7 +7009,7 @@
   <sheetFormatPr defaultColWidth="3.77777777777778" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="3.77777777777778" style="104"/>
-    <col min="2" max="2" width="5.11111111111111" style="197" customWidth="1"/>
+    <col min="2" max="2" width="5.11111111111111" style="199" customWidth="1"/>
     <col min="3" max="3" width="12.2222222222222" style="104" customWidth="1"/>
     <col min="4" max="4" width="6.88888888888889" style="104" customWidth="1"/>
     <col min="5" max="5" width="66.1111111111111" style="104" customWidth="1"/>
@@ -6999,10 +7020,10 @@
       <c r="A1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="197"/>
+      <c r="B1" s="199"/>
     </row>
     <row r="2" s="104" customFormat="1" spans="2:5">
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="200" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="115" t="s">
@@ -7016,416 +7037,416 @@
       </c>
     </row>
     <row r="3" s="104" customFormat="1" spans="2:5">
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="200">
+      <c r="C3" s="202">
         <v>45636</v>
       </c>
-      <c r="D3" s="201" t="s">
+      <c r="D3" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="201" t="s">
+      <c r="E3" s="203" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" s="104" customFormat="1" ht="66" spans="2:5">
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="201" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="200">
+      <c r="C4" s="202">
         <v>45735</v>
       </c>
-      <c r="D4" s="201" t="s">
+      <c r="D4" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="202" t="s">
+      <c r="E4" s="204" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" s="104" customFormat="1" spans="2:5">
-      <c r="B5" s="199"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="201"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="203"/>
     </row>
     <row r="6" s="104" customFormat="1" spans="2:5">
-      <c r="B6" s="199"/>
-      <c r="C6" s="201"/>
-      <c r="D6" s="201"/>
-      <c r="E6" s="201"/>
+      <c r="B6" s="201"/>
+      <c r="C6" s="203"/>
+      <c r="D6" s="203"/>
+      <c r="E6" s="203"/>
     </row>
     <row r="7" s="104" customFormat="1" spans="2:5">
-      <c r="B7" s="199"/>
-      <c r="C7" s="201"/>
-      <c r="D7" s="201"/>
-      <c r="E7" s="201"/>
+      <c r="B7" s="201"/>
+      <c r="C7" s="203"/>
+      <c r="D7" s="203"/>
+      <c r="E7" s="203"/>
     </row>
     <row r="8" s="104" customFormat="1" spans="2:5">
-      <c r="B8" s="199"/>
-      <c r="C8" s="201"/>
-      <c r="D8" s="201"/>
-      <c r="E8" s="201"/>
+      <c r="B8" s="201"/>
+      <c r="C8" s="203"/>
+      <c r="D8" s="203"/>
+      <c r="E8" s="203"/>
     </row>
     <row r="9" s="104" customFormat="1" spans="2:5">
-      <c r="B9" s="199"/>
-      <c r="C9" s="201"/>
-      <c r="D9" s="201"/>
-      <c r="E9" s="201"/>
+      <c r="B9" s="201"/>
+      <c r="C9" s="203"/>
+      <c r="D9" s="203"/>
+      <c r="E9" s="203"/>
     </row>
     <row r="10" s="104" customFormat="1" spans="2:5">
-      <c r="B10" s="199"/>
-      <c r="C10" s="201"/>
-      <c r="D10" s="201"/>
-      <c r="E10" s="201"/>
+      <c r="B10" s="201"/>
+      <c r="C10" s="203"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="203"/>
     </row>
     <row r="11" s="104" customFormat="1" spans="2:5">
-      <c r="B11" s="199"/>
-      <c r="C11" s="201"/>
-      <c r="D11" s="201"/>
-      <c r="E11" s="201"/>
+      <c r="B11" s="201"/>
+      <c r="C11" s="203"/>
+      <c r="D11" s="203"/>
+      <c r="E11" s="203"/>
     </row>
     <row r="12" s="104" customFormat="1" spans="2:5">
-      <c r="B12" s="199"/>
-      <c r="C12" s="201"/>
-      <c r="D12" s="201"/>
-      <c r="E12" s="201"/>
+      <c r="B12" s="201"/>
+      <c r="C12" s="203"/>
+      <c r="D12" s="203"/>
+      <c r="E12" s="203"/>
     </row>
     <row r="13" s="104" customFormat="1" spans="2:5">
-      <c r="B13" s="199"/>
-      <c r="C13" s="201"/>
-      <c r="D13" s="201"/>
-      <c r="E13" s="201"/>
+      <c r="B13" s="201"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
     </row>
     <row r="14" s="104" customFormat="1" spans="2:5">
-      <c r="B14" s="199"/>
-      <c r="C14" s="201"/>
-      <c r="D14" s="201"/>
-      <c r="E14" s="201"/>
+      <c r="B14" s="201"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
     </row>
     <row r="15" s="104" customFormat="1" spans="2:5">
-      <c r="B15" s="199"/>
-      <c r="C15" s="201"/>
-      <c r="D15" s="201"/>
-      <c r="E15" s="201"/>
+      <c r="B15" s="201"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
     </row>
     <row r="16" s="104" customFormat="1" spans="2:5">
-      <c r="B16" s="199"/>
-      <c r="C16" s="201"/>
-      <c r="D16" s="201"/>
-      <c r="E16" s="201"/>
+      <c r="B16" s="201"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="203"/>
     </row>
     <row r="17" s="104" customFormat="1" spans="2:5">
-      <c r="B17" s="199"/>
-      <c r="C17" s="201"/>
-      <c r="D17" s="201"/>
-      <c r="E17" s="201"/>
+      <c r="B17" s="201"/>
+      <c r="C17" s="203"/>
+      <c r="D17" s="203"/>
+      <c r="E17" s="203"/>
     </row>
     <row r="18" s="104" customFormat="1" spans="2:5">
-      <c r="B18" s="199"/>
-      <c r="C18" s="201"/>
-      <c r="D18" s="201"/>
-      <c r="E18" s="201"/>
+      <c r="B18" s="201"/>
+      <c r="C18" s="203"/>
+      <c r="D18" s="203"/>
+      <c r="E18" s="203"/>
     </row>
     <row r="19" s="104" customFormat="1" spans="2:5">
-      <c r="B19" s="199"/>
-      <c r="C19" s="201"/>
-      <c r="D19" s="201"/>
-      <c r="E19" s="201"/>
+      <c r="B19" s="201"/>
+      <c r="C19" s="203"/>
+      <c r="D19" s="203"/>
+      <c r="E19" s="203"/>
     </row>
     <row r="20" s="104" customFormat="1" spans="2:5">
-      <c r="B20" s="199"/>
-      <c r="C20" s="201"/>
-      <c r="D20" s="201"/>
-      <c r="E20" s="201"/>
+      <c r="B20" s="201"/>
+      <c r="C20" s="203"/>
+      <c r="D20" s="203"/>
+      <c r="E20" s="203"/>
     </row>
     <row r="21" s="104" customFormat="1" spans="2:5">
-      <c r="B21" s="199"/>
-      <c r="C21" s="201"/>
-      <c r="D21" s="201"/>
-      <c r="E21" s="201"/>
+      <c r="B21" s="201"/>
+      <c r="C21" s="203"/>
+      <c r="D21" s="203"/>
+      <c r="E21" s="203"/>
     </row>
     <row r="22" s="104" customFormat="1" spans="2:5">
-      <c r="B22" s="199"/>
-      <c r="C22" s="201"/>
-      <c r="D22" s="201"/>
-      <c r="E22" s="201"/>
+      <c r="B22" s="201"/>
+      <c r="C22" s="203"/>
+      <c r="D22" s="203"/>
+      <c r="E22" s="203"/>
     </row>
     <row r="23" s="104" customFormat="1" spans="2:5">
-      <c r="B23" s="199"/>
-      <c r="C23" s="201"/>
-      <c r="D23" s="201"/>
-      <c r="E23" s="201"/>
+      <c r="B23" s="201"/>
+      <c r="C23" s="203"/>
+      <c r="D23" s="203"/>
+      <c r="E23" s="203"/>
     </row>
     <row r="24" s="104" customFormat="1" spans="2:5">
-      <c r="B24" s="199"/>
-      <c r="C24" s="201"/>
-      <c r="D24" s="201"/>
-      <c r="E24" s="201"/>
+      <c r="B24" s="201"/>
+      <c r="C24" s="203"/>
+      <c r="D24" s="203"/>
+      <c r="E24" s="203"/>
     </row>
     <row r="25" s="104" customFormat="1" spans="2:5">
-      <c r="B25" s="199"/>
-      <c r="C25" s="201"/>
-      <c r="D25" s="201"/>
-      <c r="E25" s="201"/>
+      <c r="B25" s="201"/>
+      <c r="C25" s="203"/>
+      <c r="D25" s="203"/>
+      <c r="E25" s="203"/>
     </row>
     <row r="26" s="104" customFormat="1" spans="2:5">
-      <c r="B26" s="199"/>
-      <c r="C26" s="201"/>
-      <c r="D26" s="201"/>
-      <c r="E26" s="201"/>
+      <c r="B26" s="201"/>
+      <c r="C26" s="203"/>
+      <c r="D26" s="203"/>
+      <c r="E26" s="203"/>
     </row>
     <row r="27" s="104" customFormat="1" spans="2:5">
-      <c r="B27" s="199"/>
-      <c r="C27" s="201"/>
-      <c r="D27" s="201"/>
-      <c r="E27" s="201"/>
+      <c r="B27" s="201"/>
+      <c r="C27" s="203"/>
+      <c r="D27" s="203"/>
+      <c r="E27" s="203"/>
     </row>
     <row r="28" s="104" customFormat="1" spans="2:5">
-      <c r="B28" s="199"/>
-      <c r="C28" s="201"/>
-      <c r="D28" s="201"/>
-      <c r="E28" s="201"/>
+      <c r="B28" s="201"/>
+      <c r="C28" s="203"/>
+      <c r="D28" s="203"/>
+      <c r="E28" s="203"/>
     </row>
     <row r="29" s="104" customFormat="1" spans="2:5">
-      <c r="B29" s="199"/>
-      <c r="C29" s="201"/>
-      <c r="D29" s="201"/>
-      <c r="E29" s="201"/>
+      <c r="B29" s="201"/>
+      <c r="C29" s="203"/>
+      <c r="D29" s="203"/>
+      <c r="E29" s="203"/>
     </row>
     <row r="30" s="104" customFormat="1" spans="2:5">
-      <c r="B30" s="199"/>
-      <c r="C30" s="201"/>
-      <c r="D30" s="201"/>
-      <c r="E30" s="201"/>
+      <c r="B30" s="201"/>
+      <c r="C30" s="203"/>
+      <c r="D30" s="203"/>
+      <c r="E30" s="203"/>
     </row>
     <row r="31" s="104" customFormat="1" spans="2:5">
-      <c r="B31" s="199"/>
-      <c r="C31" s="201"/>
-      <c r="D31" s="201"/>
-      <c r="E31" s="201"/>
+      <c r="B31" s="201"/>
+      <c r="C31" s="203"/>
+      <c r="D31" s="203"/>
+      <c r="E31" s="203"/>
     </row>
     <row r="32" s="104" customFormat="1" spans="2:5">
-      <c r="B32" s="199"/>
-      <c r="C32" s="201"/>
-      <c r="D32" s="201"/>
-      <c r="E32" s="201"/>
+      <c r="B32" s="201"/>
+      <c r="C32" s="203"/>
+      <c r="D32" s="203"/>
+      <c r="E32" s="203"/>
     </row>
     <row r="33" s="104" customFormat="1" spans="2:5">
-      <c r="B33" s="199"/>
-      <c r="C33" s="201"/>
-      <c r="D33" s="201"/>
-      <c r="E33" s="201"/>
+      <c r="B33" s="201"/>
+      <c r="C33" s="203"/>
+      <c r="D33" s="203"/>
+      <c r="E33" s="203"/>
     </row>
     <row r="34" s="104" customFormat="1" spans="2:5">
-      <c r="B34" s="199"/>
-      <c r="C34" s="201"/>
-      <c r="D34" s="201"/>
-      <c r="E34" s="201"/>
+      <c r="B34" s="201"/>
+      <c r="C34" s="203"/>
+      <c r="D34" s="203"/>
+      <c r="E34" s="203"/>
     </row>
     <row r="35" s="104" customFormat="1" spans="2:5">
-      <c r="B35" s="199"/>
-      <c r="C35" s="201"/>
-      <c r="D35" s="201"/>
-      <c r="E35" s="201"/>
+      <c r="B35" s="201"/>
+      <c r="C35" s="203"/>
+      <c r="D35" s="203"/>
+      <c r="E35" s="203"/>
     </row>
     <row r="36" s="104" customFormat="1" spans="2:5">
-      <c r="B36" s="199"/>
-      <c r="C36" s="201"/>
-      <c r="D36" s="201"/>
-      <c r="E36" s="201"/>
+      <c r="B36" s="201"/>
+      <c r="C36" s="203"/>
+      <c r="D36" s="203"/>
+      <c r="E36" s="203"/>
     </row>
     <row r="37" s="104" customFormat="1" spans="2:5">
-      <c r="B37" s="199"/>
-      <c r="C37" s="201"/>
-      <c r="D37" s="201"/>
-      <c r="E37" s="201"/>
+      <c r="B37" s="201"/>
+      <c r="C37" s="203"/>
+      <c r="D37" s="203"/>
+      <c r="E37" s="203"/>
     </row>
     <row r="38" s="104" customFormat="1" spans="2:5">
-      <c r="B38" s="199"/>
-      <c r="C38" s="201"/>
-      <c r="D38" s="201"/>
-      <c r="E38" s="201"/>
+      <c r="B38" s="201"/>
+      <c r="C38" s="203"/>
+      <c r="D38" s="203"/>
+      <c r="E38" s="203"/>
     </row>
     <row r="39" s="104" customFormat="1" spans="2:5">
-      <c r="B39" s="199"/>
-      <c r="C39" s="201"/>
-      <c r="D39" s="201"/>
-      <c r="E39" s="201"/>
+      <c r="B39" s="201"/>
+      <c r="C39" s="203"/>
+      <c r="D39" s="203"/>
+      <c r="E39" s="203"/>
     </row>
     <row r="40" s="104" customFormat="1" spans="2:5">
-      <c r="B40" s="199"/>
-      <c r="C40" s="201"/>
-      <c r="D40" s="201"/>
-      <c r="E40" s="201"/>
+      <c r="B40" s="201"/>
+      <c r="C40" s="203"/>
+      <c r="D40" s="203"/>
+      <c r="E40" s="203"/>
     </row>
     <row r="41" s="104" customFormat="1" spans="2:5">
-      <c r="B41" s="199"/>
-      <c r="C41" s="201"/>
-      <c r="D41" s="201"/>
-      <c r="E41" s="201"/>
+      <c r="B41" s="201"/>
+      <c r="C41" s="203"/>
+      <c r="D41" s="203"/>
+      <c r="E41" s="203"/>
     </row>
     <row r="42" s="104" customFormat="1" spans="2:5">
-      <c r="B42" s="199"/>
-      <c r="C42" s="201"/>
-      <c r="D42" s="201"/>
-      <c r="E42" s="201"/>
+      <c r="B42" s="201"/>
+      <c r="C42" s="203"/>
+      <c r="D42" s="203"/>
+      <c r="E42" s="203"/>
     </row>
     <row r="43" s="104" customFormat="1" spans="2:5">
-      <c r="B43" s="199"/>
-      <c r="C43" s="201"/>
-      <c r="D43" s="201"/>
-      <c r="E43" s="201"/>
+      <c r="B43" s="201"/>
+      <c r="C43" s="203"/>
+      <c r="D43" s="203"/>
+      <c r="E43" s="203"/>
     </row>
     <row r="44" s="104" customFormat="1" spans="2:5">
-      <c r="B44" s="199"/>
-      <c r="C44" s="201"/>
-      <c r="D44" s="201"/>
-      <c r="E44" s="201"/>
+      <c r="B44" s="201"/>
+      <c r="C44" s="203"/>
+      <c r="D44" s="203"/>
+      <c r="E44" s="203"/>
     </row>
     <row r="45" s="104" customFormat="1" spans="2:5">
-      <c r="B45" s="199"/>
-      <c r="C45" s="201"/>
-      <c r="D45" s="201"/>
-      <c r="E45" s="201"/>
+      <c r="B45" s="201"/>
+      <c r="C45" s="203"/>
+      <c r="D45" s="203"/>
+      <c r="E45" s="203"/>
     </row>
     <row r="46" s="104" customFormat="1" spans="2:5">
-      <c r="B46" s="199"/>
-      <c r="C46" s="201"/>
-      <c r="D46" s="201"/>
-      <c r="E46" s="201"/>
+      <c r="B46" s="201"/>
+      <c r="C46" s="203"/>
+      <c r="D46" s="203"/>
+      <c r="E46" s="203"/>
     </row>
     <row r="47" s="104" customFormat="1" spans="2:5">
-      <c r="B47" s="199"/>
-      <c r="C47" s="201"/>
-      <c r="D47" s="201"/>
-      <c r="E47" s="201"/>
+      <c r="B47" s="201"/>
+      <c r="C47" s="203"/>
+      <c r="D47" s="203"/>
+      <c r="E47" s="203"/>
     </row>
     <row r="48" s="104" customFormat="1" spans="2:5">
-      <c r="B48" s="199"/>
-      <c r="C48" s="201"/>
-      <c r="D48" s="201"/>
-      <c r="E48" s="201"/>
+      <c r="B48" s="201"/>
+      <c r="C48" s="203"/>
+      <c r="D48" s="203"/>
+      <c r="E48" s="203"/>
     </row>
     <row r="49" s="104" customFormat="1" spans="2:5">
-      <c r="B49" s="199"/>
-      <c r="C49" s="201"/>
-      <c r="D49" s="201"/>
-      <c r="E49" s="201"/>
+      <c r="B49" s="201"/>
+      <c r="C49" s="203"/>
+      <c r="D49" s="203"/>
+      <c r="E49" s="203"/>
     </row>
     <row r="50" s="104" customFormat="1" spans="2:5">
-      <c r="B50" s="199"/>
-      <c r="C50" s="201"/>
-      <c r="D50" s="201"/>
-      <c r="E50" s="201"/>
+      <c r="B50" s="201"/>
+      <c r="C50" s="203"/>
+      <c r="D50" s="203"/>
+      <c r="E50" s="203"/>
     </row>
     <row r="51" s="104" customFormat="1" spans="2:5">
-      <c r="B51" s="199"/>
-      <c r="C51" s="201"/>
-      <c r="D51" s="201"/>
-      <c r="E51" s="201"/>
+      <c r="B51" s="201"/>
+      <c r="C51" s="203"/>
+      <c r="D51" s="203"/>
+      <c r="E51" s="203"/>
     </row>
     <row r="52" s="104" customFormat="1" spans="2:5">
-      <c r="B52" s="199"/>
-      <c r="C52" s="201"/>
-      <c r="D52" s="201"/>
-      <c r="E52" s="201"/>
+      <c r="B52" s="201"/>
+      <c r="C52" s="203"/>
+      <c r="D52" s="203"/>
+      <c r="E52" s="203"/>
     </row>
     <row r="53" s="104" customFormat="1" spans="2:5">
-      <c r="B53" s="199"/>
-      <c r="C53" s="201"/>
-      <c r="D53" s="201"/>
-      <c r="E53" s="201"/>
+      <c r="B53" s="201"/>
+      <c r="C53" s="203"/>
+      <c r="D53" s="203"/>
+      <c r="E53" s="203"/>
     </row>
     <row r="54" s="104" customFormat="1" spans="2:5">
-      <c r="B54" s="199"/>
-      <c r="C54" s="201"/>
-      <c r="D54" s="201"/>
-      <c r="E54" s="201"/>
+      <c r="B54" s="201"/>
+      <c r="C54" s="203"/>
+      <c r="D54" s="203"/>
+      <c r="E54" s="203"/>
     </row>
     <row r="55" s="104" customFormat="1" spans="2:5">
-      <c r="B55" s="199"/>
-      <c r="C55" s="201"/>
-      <c r="D55" s="201"/>
-      <c r="E55" s="201"/>
+      <c r="B55" s="201"/>
+      <c r="C55" s="203"/>
+      <c r="D55" s="203"/>
+      <c r="E55" s="203"/>
     </row>
     <row r="56" s="104" customFormat="1" spans="2:5">
-      <c r="B56" s="199"/>
-      <c r="C56" s="201"/>
-      <c r="D56" s="201"/>
-      <c r="E56" s="201"/>
+      <c r="B56" s="201"/>
+      <c r="C56" s="203"/>
+      <c r="D56" s="203"/>
+      <c r="E56" s="203"/>
     </row>
     <row r="57" s="104" customFormat="1" spans="2:5">
-      <c r="B57" s="199"/>
-      <c r="C57" s="201"/>
-      <c r="D57" s="201"/>
-      <c r="E57" s="201"/>
+      <c r="B57" s="201"/>
+      <c r="C57" s="203"/>
+      <c r="D57" s="203"/>
+      <c r="E57" s="203"/>
     </row>
     <row r="58" s="104" customFormat="1" spans="2:5">
-      <c r="B58" s="199"/>
-      <c r="C58" s="201"/>
-      <c r="D58" s="201"/>
-      <c r="E58" s="201"/>
+      <c r="B58" s="201"/>
+      <c r="C58" s="203"/>
+      <c r="D58" s="203"/>
+      <c r="E58" s="203"/>
     </row>
     <row r="59" s="104" customFormat="1" spans="2:5">
-      <c r="B59" s="199"/>
-      <c r="C59" s="201"/>
-      <c r="D59" s="201"/>
-      <c r="E59" s="201"/>
+      <c r="B59" s="201"/>
+      <c r="C59" s="203"/>
+      <c r="D59" s="203"/>
+      <c r="E59" s="203"/>
     </row>
     <row r="60" s="104" customFormat="1" spans="2:5">
-      <c r="B60" s="199"/>
-      <c r="C60" s="201"/>
-      <c r="D60" s="201"/>
-      <c r="E60" s="201"/>
+      <c r="B60" s="201"/>
+      <c r="C60" s="203"/>
+      <c r="D60" s="203"/>
+      <c r="E60" s="203"/>
     </row>
     <row r="61" s="104" customFormat="1" spans="2:5">
-      <c r="B61" s="199"/>
-      <c r="C61" s="201"/>
-      <c r="D61" s="201"/>
-      <c r="E61" s="201"/>
+      <c r="B61" s="201"/>
+      <c r="C61" s="203"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="203"/>
     </row>
     <row r="62" s="104" customFormat="1" spans="2:5">
-      <c r="B62" s="199"/>
-      <c r="C62" s="201"/>
-      <c r="D62" s="201"/>
-      <c r="E62" s="201"/>
+      <c r="B62" s="201"/>
+      <c r="C62" s="203"/>
+      <c r="D62" s="203"/>
+      <c r="E62" s="203"/>
     </row>
     <row r="63" s="104" customFormat="1" spans="2:5">
-      <c r="B63" s="199"/>
-      <c r="C63" s="201"/>
-      <c r="D63" s="201"/>
-      <c r="E63" s="201"/>
+      <c r="B63" s="201"/>
+      <c r="C63" s="203"/>
+      <c r="D63" s="203"/>
+      <c r="E63" s="203"/>
     </row>
     <row r="64" s="104" customFormat="1" spans="2:5">
-      <c r="B64" s="199"/>
-      <c r="C64" s="201"/>
-      <c r="D64" s="201"/>
-      <c r="E64" s="201"/>
+      <c r="B64" s="201"/>
+      <c r="C64" s="203"/>
+      <c r="D64" s="203"/>
+      <c r="E64" s="203"/>
     </row>
     <row r="65" s="104" customFormat="1" spans="2:5">
-      <c r="B65" s="199"/>
-      <c r="C65" s="201"/>
-      <c r="D65" s="201"/>
-      <c r="E65" s="201"/>
+      <c r="B65" s="201"/>
+      <c r="C65" s="203"/>
+      <c r="D65" s="203"/>
+      <c r="E65" s="203"/>
     </row>
     <row r="66" s="104" customFormat="1" spans="2:5">
-      <c r="B66" s="199"/>
-      <c r="C66" s="201"/>
-      <c r="D66" s="201"/>
-      <c r="E66" s="201"/>
+      <c r="B66" s="201"/>
+      <c r="C66" s="203"/>
+      <c r="D66" s="203"/>
+      <c r="E66" s="203"/>
     </row>
     <row r="67" s="104" customFormat="1" spans="2:5">
-      <c r="B67" s="199"/>
-      <c r="C67" s="201"/>
-      <c r="D67" s="201"/>
-      <c r="E67" s="201"/>
+      <c r="B67" s="201"/>
+      <c r="C67" s="203"/>
+      <c r="D67" s="203"/>
+      <c r="E67" s="203"/>
     </row>
     <row r="68" s="104" customFormat="1" spans="2:5">
-      <c r="B68" s="199"/>
-      <c r="C68" s="201"/>
-      <c r="D68" s="201"/>
-      <c r="E68" s="201"/>
+      <c r="B68" s="201"/>
+      <c r="C68" s="203"/>
+      <c r="D68" s="203"/>
+      <c r="E68" s="203"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7481,23 +7502,23 @@
       </c>
       <c r="AC1" s="115"/>
       <c r="AD1" s="115"/>
-      <c r="AE1" s="190" t="s">
+      <c r="AE1" s="192" t="s">
         <v>6</v>
       </c>
-      <c r="AF1" s="190"/>
-      <c r="AG1" s="190"/>
-      <c r="AH1" s="190"/>
+      <c r="AF1" s="192"/>
+      <c r="AG1" s="192"/>
+      <c r="AH1" s="192"/>
       <c r="AI1" s="115" t="s">
         <v>13</v>
       </c>
       <c r="AJ1" s="115"/>
       <c r="AK1" s="115"/>
-      <c r="AL1" s="195">
+      <c r="AL1" s="197">
         <v>45566</v>
       </c>
-      <c r="AM1" s="190"/>
-      <c r="AN1" s="190"/>
-      <c r="AO1" s="190"/>
+      <c r="AM1" s="192"/>
+      <c r="AN1" s="192"/>
+      <c r="AO1" s="192"/>
     </row>
     <row r="2" customHeight="1" spans="1:41">
       <c r="A2" s="4"/>
@@ -7534,17 +7555,17 @@
       <c r="AB2" s="115"/>
       <c r="AC2" s="115"/>
       <c r="AD2" s="115"/>
-      <c r="AE2" s="190"/>
-      <c r="AF2" s="190"/>
-      <c r="AG2" s="190"/>
-      <c r="AH2" s="190"/>
+      <c r="AE2" s="192"/>
+      <c r="AF2" s="192"/>
+      <c r="AG2" s="192"/>
+      <c r="AH2" s="192"/>
       <c r="AI2" s="115"/>
       <c r="AJ2" s="115"/>
       <c r="AK2" s="115"/>
-      <c r="AL2" s="190"/>
-      <c r="AM2" s="190"/>
-      <c r="AN2" s="190"/>
-      <c r="AO2" s="190"/>
+      <c r="AL2" s="192"/>
+      <c r="AM2" s="192"/>
+      <c r="AN2" s="192"/>
+      <c r="AO2" s="192"/>
     </row>
     <row r="3" customHeight="1" spans="1:41">
       <c r="A3" s="4"/>
@@ -7568,34 +7589,34 @@
       <c r="Q3" s="115"/>
       <c r="R3" s="115"/>
       <c r="S3" s="115"/>
-      <c r="T3" s="190" t="s">
+      <c r="T3" s="192" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="190"/>
-      <c r="V3" s="190"/>
-      <c r="W3" s="190"/>
-      <c r="X3" s="190"/>
-      <c r="Y3" s="190"/>
-      <c r="Z3" s="190"/>
-      <c r="AA3" s="190"/>
+      <c r="U3" s="192"/>
+      <c r="V3" s="192"/>
+      <c r="W3" s="192"/>
+      <c r="X3" s="192"/>
+      <c r="Y3" s="192"/>
+      <c r="Z3" s="192"/>
+      <c r="AA3" s="192"/>
       <c r="AB3" s="115" t="s">
         <v>18</v>
       </c>
       <c r="AC3" s="115"/>
       <c r="AD3" s="115"/>
-      <c r="AE3" s="190"/>
-      <c r="AF3" s="190"/>
-      <c r="AG3" s="190"/>
-      <c r="AH3" s="190"/>
+      <c r="AE3" s="192"/>
+      <c r="AF3" s="192"/>
+      <c r="AG3" s="192"/>
+      <c r="AH3" s="192"/>
       <c r="AI3" s="115" t="s">
         <v>19</v>
       </c>
       <c r="AJ3" s="115"/>
       <c r="AK3" s="115"/>
-      <c r="AL3" s="190"/>
-      <c r="AM3" s="190"/>
-      <c r="AN3" s="190"/>
-      <c r="AO3" s="190"/>
+      <c r="AL3" s="192"/>
+      <c r="AM3" s="192"/>
+      <c r="AN3" s="192"/>
+      <c r="AO3" s="192"/>
     </row>
     <row r="4" customHeight="1" spans="1:41">
       <c r="A4" s="6"/>
@@ -7619,30 +7640,30 @@
       <c r="Q4" s="115"/>
       <c r="R4" s="115"/>
       <c r="S4" s="115"/>
-      <c r="T4" s="190" t="s">
+      <c r="T4" s="192" t="s">
         <v>21</v>
       </c>
-      <c r="U4" s="190"/>
-      <c r="V4" s="190"/>
-      <c r="W4" s="190"/>
-      <c r="X4" s="190"/>
-      <c r="Y4" s="190"/>
-      <c r="Z4" s="190"/>
-      <c r="AA4" s="190"/>
+      <c r="U4" s="192"/>
+      <c r="V4" s="192"/>
+      <c r="W4" s="192"/>
+      <c r="X4" s="192"/>
+      <c r="Y4" s="192"/>
+      <c r="Z4" s="192"/>
+      <c r="AA4" s="192"/>
       <c r="AB4" s="115"/>
       <c r="AC4" s="115"/>
       <c r="AD4" s="115"/>
-      <c r="AE4" s="190"/>
-      <c r="AF4" s="190"/>
-      <c r="AG4" s="190"/>
-      <c r="AH4" s="190"/>
+      <c r="AE4" s="192"/>
+      <c r="AF4" s="192"/>
+      <c r="AG4" s="192"/>
+      <c r="AH4" s="192"/>
       <c r="AI4" s="115"/>
       <c r="AJ4" s="115"/>
       <c r="AK4" s="115"/>
-      <c r="AL4" s="190"/>
-      <c r="AM4" s="190"/>
-      <c r="AN4" s="190"/>
-      <c r="AO4" s="190"/>
+      <c r="AL4" s="192"/>
+      <c r="AM4" s="192"/>
+      <c r="AN4" s="192"/>
+      <c r="AO4" s="192"/>
     </row>
     <row r="5" customHeight="1" spans="1:41">
       <c r="A5" s="98" t="s">
@@ -7694,28 +7715,28 @@
       <c r="AO5" s="98"/>
     </row>
     <row r="6" customHeight="1" spans="1:41">
-      <c r="A6" s="188"/>
-      <c r="B6" s="189"/>
-      <c r="C6" s="189"/>
-      <c r="D6" s="189"/>
-      <c r="E6" s="189"/>
-      <c r="F6" s="189"/>
-      <c r="G6" s="189"/>
-      <c r="H6" s="189"/>
-      <c r="I6" s="189"/>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
-      <c r="M6" s="189"/>
-      <c r="N6" s="189"/>
-      <c r="O6" s="189"/>
-      <c r="P6" s="189"/>
-      <c r="Q6" s="189"/>
-      <c r="R6" s="189"/>
-      <c r="S6" s="189"/>
-      <c r="T6" s="189"/>
-      <c r="U6" s="189"/>
-      <c r="V6" s="193"/>
+      <c r="A6" s="190"/>
+      <c r="B6" s="191"/>
+      <c r="C6" s="191"/>
+      <c r="D6" s="191"/>
+      <c r="E6" s="191"/>
+      <c r="F6" s="191"/>
+      <c r="G6" s="191"/>
+      <c r="H6" s="191"/>
+      <c r="I6" s="191"/>
+      <c r="J6" s="191"/>
+      <c r="K6" s="191"/>
+      <c r="L6" s="191"/>
+      <c r="M6" s="191"/>
+      <c r="N6" s="191"/>
+      <c r="O6" s="191"/>
+      <c r="P6" s="191"/>
+      <c r="Q6" s="191"/>
+      <c r="R6" s="191"/>
+      <c r="S6" s="191"/>
+      <c r="T6" s="191"/>
+      <c r="U6" s="191"/>
+      <c r="V6" s="195"/>
       <c r="W6" s="8" t="s">
         <v>24</v>
       </c>
@@ -7734,9 +7755,9 @@
       <c r="AJ6" s="9"/>
       <c r="AK6" s="9"/>
       <c r="AL6" s="43"/>
-      <c r="AM6" s="188"/>
-      <c r="AN6" s="189"/>
-      <c r="AO6" s="193"/>
+      <c r="AM6" s="190"/>
+      <c r="AN6" s="191"/>
+      <c r="AO6" s="195"/>
     </row>
     <row r="7" customHeight="1" spans="1:41">
       <c r="A7" s="128"/>
@@ -7765,7 +7786,7 @@
     <row r="8" customHeight="1" spans="1:41">
       <c r="A8" s="128"/>
       <c r="V8" s="141"/>
-      <c r="W8" s="1" t="s">
+      <c r="W8" s="12" t="s">
         <v>26</v>
       </c>
       <c r="AM8" s="128"/>
@@ -7841,7 +7862,7 @@
       <c r="A12" s="128"/>
       <c r="V12" s="141"/>
       <c r="W12" s="10"/>
-      <c r="X12" s="194"/>
+      <c r="X12" s="196"/>
       <c r="Y12" s="12"/>
       <c r="Z12" s="12"/>
       <c r="AA12" s="12"/>
@@ -8094,534 +8115,534 @@
       <c r="AO20" s="49"/>
     </row>
     <row r="21" customHeight="1" spans="1:41">
-      <c r="A21" s="190">
+      <c r="A21" s="192">
         <v>1</v>
       </c>
       <c r="B21" s="23"/>
-      <c r="C21" s="191" t="s">
+      <c r="C21" s="193" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="192"/>
-      <c r="E21" s="192"/>
-      <c r="F21" s="192"/>
-      <c r="G21" s="192"/>
-      <c r="H21" s="192"/>
-      <c r="I21" s="192"/>
-      <c r="J21" s="192"/>
-      <c r="K21" s="190" t="s">
+      <c r="D21" s="194"/>
+      <c r="E21" s="194"/>
+      <c r="F21" s="194"/>
+      <c r="G21" s="194"/>
+      <c r="H21" s="194"/>
+      <c r="I21" s="194"/>
+      <c r="J21" s="194"/>
+      <c r="K21" s="192" t="s">
         <v>36</v>
       </c>
-      <c r="L21" s="190"/>
-      <c r="M21" s="190" t="s">
+      <c r="L21" s="192"/>
+      <c r="M21" s="192" t="s">
         <v>37</v>
       </c>
-      <c r="N21" s="190" t="s">
+      <c r="N21" s="192" t="s">
         <v>38</v>
       </c>
-      <c r="O21" s="190" t="s">
+      <c r="O21" s="192" t="s">
         <v>37</v>
       </c>
-      <c r="P21" s="190" t="s">
+      <c r="P21" s="192" t="s">
         <v>37</v>
       </c>
-      <c r="Q21" s="191"/>
-      <c r="R21" s="192"/>
-      <c r="S21" s="192"/>
-      <c r="T21" s="192"/>
-      <c r="U21" s="192"/>
-      <c r="V21" s="192"/>
-      <c r="W21" s="192"/>
-      <c r="X21" s="192"/>
-      <c r="Y21" s="192"/>
-      <c r="Z21" s="192"/>
-      <c r="AA21" s="192"/>
-      <c r="AB21" s="192"/>
-      <c r="AC21" s="192"/>
-      <c r="AD21" s="192"/>
-      <c r="AE21" s="192"/>
-      <c r="AF21" s="192"/>
-      <c r="AG21" s="192"/>
-      <c r="AH21" s="192"/>
-      <c r="AI21" s="192"/>
-      <c r="AJ21" s="192"/>
-      <c r="AK21" s="192"/>
-      <c r="AL21" s="192"/>
-      <c r="AM21" s="192"/>
-      <c r="AN21" s="192"/>
-      <c r="AO21" s="196"/>
+      <c r="Q21" s="193"/>
+      <c r="R21" s="194"/>
+      <c r="S21" s="194"/>
+      <c r="T21" s="194"/>
+      <c r="U21" s="194"/>
+      <c r="V21" s="194"/>
+      <c r="W21" s="194"/>
+      <c r="X21" s="194"/>
+      <c r="Y21" s="194"/>
+      <c r="Z21" s="194"/>
+      <c r="AA21" s="194"/>
+      <c r="AB21" s="194"/>
+      <c r="AC21" s="194"/>
+      <c r="AD21" s="194"/>
+      <c r="AE21" s="194"/>
+      <c r="AF21" s="194"/>
+      <c r="AG21" s="194"/>
+      <c r="AH21" s="194"/>
+      <c r="AI21" s="194"/>
+      <c r="AJ21" s="194"/>
+      <c r="AK21" s="194"/>
+      <c r="AL21" s="194"/>
+      <c r="AM21" s="194"/>
+      <c r="AN21" s="194"/>
+      <c r="AO21" s="198"/>
     </row>
     <row r="22" customHeight="1" spans="1:41">
-      <c r="A22" s="190"/>
+      <c r="A22" s="192"/>
       <c r="B22" s="23"/>
-      <c r="C22" s="191"/>
-      <c r="D22" s="192"/>
-      <c r="E22" s="192"/>
-      <c r="F22" s="192"/>
-      <c r="G22" s="192"/>
-      <c r="H22" s="192"/>
-      <c r="I22" s="192"/>
-      <c r="J22" s="192"/>
-      <c r="K22" s="190"/>
-      <c r="L22" s="190"/>
-      <c r="M22" s="190"/>
-      <c r="N22" s="190"/>
-      <c r="O22" s="190"/>
-      <c r="P22" s="190"/>
-      <c r="Q22" s="191"/>
-      <c r="R22" s="192"/>
-      <c r="S22" s="192"/>
-      <c r="T22" s="192"/>
-      <c r="U22" s="192"/>
-      <c r="V22" s="192"/>
-      <c r="W22" s="192"/>
-      <c r="X22" s="192"/>
-      <c r="Y22" s="192"/>
-      <c r="Z22" s="192"/>
-      <c r="AA22" s="192"/>
-      <c r="AB22" s="192"/>
-      <c r="AC22" s="192"/>
-      <c r="AD22" s="192"/>
-      <c r="AE22" s="192"/>
-      <c r="AF22" s="192"/>
-      <c r="AG22" s="192"/>
-      <c r="AH22" s="192"/>
-      <c r="AI22" s="192"/>
-      <c r="AJ22" s="192"/>
-      <c r="AK22" s="192"/>
-      <c r="AL22" s="192"/>
-      <c r="AM22" s="192"/>
-      <c r="AN22" s="192"/>
-      <c r="AO22" s="196"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="194"/>
+      <c r="E22" s="194"/>
+      <c r="F22" s="194"/>
+      <c r="G22" s="194"/>
+      <c r="H22" s="194"/>
+      <c r="I22" s="194"/>
+      <c r="J22" s="194"/>
+      <c r="K22" s="192"/>
+      <c r="L22" s="192"/>
+      <c r="M22" s="192"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="192"/>
+      <c r="P22" s="192"/>
+      <c r="Q22" s="193"/>
+      <c r="R22" s="194"/>
+      <c r="S22" s="194"/>
+      <c r="T22" s="194"/>
+      <c r="U22" s="194"/>
+      <c r="V22" s="194"/>
+      <c r="W22" s="194"/>
+      <c r="X22" s="194"/>
+      <c r="Y22" s="194"/>
+      <c r="Z22" s="194"/>
+      <c r="AA22" s="194"/>
+      <c r="AB22" s="194"/>
+      <c r="AC22" s="194"/>
+      <c r="AD22" s="194"/>
+      <c r="AE22" s="194"/>
+      <c r="AF22" s="194"/>
+      <c r="AG22" s="194"/>
+      <c r="AH22" s="194"/>
+      <c r="AI22" s="194"/>
+      <c r="AJ22" s="194"/>
+      <c r="AK22" s="194"/>
+      <c r="AL22" s="194"/>
+      <c r="AM22" s="194"/>
+      <c r="AN22" s="194"/>
+      <c r="AO22" s="198"/>
     </row>
     <row r="23" customHeight="1" spans="1:41">
-      <c r="A23" s="190"/>
+      <c r="A23" s="192"/>
       <c r="B23" s="23"/>
-      <c r="C23" s="191"/>
-      <c r="D23" s="192"/>
-      <c r="E23" s="192"/>
-      <c r="F23" s="192"/>
-      <c r="G23" s="192"/>
-      <c r="H23" s="192"/>
-      <c r="I23" s="192"/>
-      <c r="J23" s="192"/>
-      <c r="K23" s="190"/>
-      <c r="L23" s="190"/>
-      <c r="M23" s="190"/>
-      <c r="N23" s="190"/>
-      <c r="O23" s="190"/>
-      <c r="P23" s="190"/>
-      <c r="Q23" s="191"/>
-      <c r="R23" s="192"/>
-      <c r="S23" s="192"/>
-      <c r="T23" s="192"/>
-      <c r="U23" s="192"/>
-      <c r="V23" s="192"/>
-      <c r="W23" s="192"/>
-      <c r="X23" s="192"/>
-      <c r="Y23" s="192"/>
-      <c r="Z23" s="192"/>
-      <c r="AA23" s="192"/>
-      <c r="AB23" s="192"/>
-      <c r="AC23" s="192"/>
-      <c r="AD23" s="192"/>
-      <c r="AE23" s="192"/>
-      <c r="AF23" s="192"/>
-      <c r="AG23" s="192"/>
-      <c r="AH23" s="192"/>
-      <c r="AI23" s="192"/>
-      <c r="AJ23" s="192"/>
-      <c r="AK23" s="192"/>
-      <c r="AL23" s="192"/>
-      <c r="AM23" s="192"/>
-      <c r="AN23" s="192"/>
-      <c r="AO23" s="196"/>
+      <c r="C23" s="193"/>
+      <c r="D23" s="194"/>
+      <c r="E23" s="194"/>
+      <c r="F23" s="194"/>
+      <c r="G23" s="194"/>
+      <c r="H23" s="194"/>
+      <c r="I23" s="194"/>
+      <c r="J23" s="194"/>
+      <c r="K23" s="192"/>
+      <c r="L23" s="192"/>
+      <c r="M23" s="192"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="192"/>
+      <c r="P23" s="192"/>
+      <c r="Q23" s="193"/>
+      <c r="R23" s="194"/>
+      <c r="S23" s="194"/>
+      <c r="T23" s="194"/>
+      <c r="U23" s="194"/>
+      <c r="V23" s="194"/>
+      <c r="W23" s="194"/>
+      <c r="X23" s="194"/>
+      <c r="Y23" s="194"/>
+      <c r="Z23" s="194"/>
+      <c r="AA23" s="194"/>
+      <c r="AB23" s="194"/>
+      <c r="AC23" s="194"/>
+      <c r="AD23" s="194"/>
+      <c r="AE23" s="194"/>
+      <c r="AF23" s="194"/>
+      <c r="AG23" s="194"/>
+      <c r="AH23" s="194"/>
+      <c r="AI23" s="194"/>
+      <c r="AJ23" s="194"/>
+      <c r="AK23" s="194"/>
+      <c r="AL23" s="194"/>
+      <c r="AM23" s="194"/>
+      <c r="AN23" s="194"/>
+      <c r="AO23" s="198"/>
     </row>
     <row r="24" customHeight="1" spans="1:41">
-      <c r="A24" s="190"/>
-      <c r="B24" s="190"/>
-      <c r="C24" s="191"/>
-      <c r="D24" s="192"/>
-      <c r="E24" s="192"/>
-      <c r="F24" s="192"/>
-      <c r="G24" s="192"/>
-      <c r="H24" s="192"/>
-      <c r="I24" s="192"/>
-      <c r="J24" s="192"/>
-      <c r="K24" s="190"/>
-      <c r="L24" s="190"/>
-      <c r="M24" s="190"/>
-      <c r="N24" s="190"/>
-      <c r="O24" s="190"/>
-      <c r="P24" s="190"/>
-      <c r="Q24" s="191"/>
-      <c r="R24" s="192"/>
-      <c r="S24" s="192"/>
-      <c r="T24" s="192"/>
-      <c r="U24" s="192"/>
-      <c r="V24" s="192"/>
-      <c r="W24" s="192"/>
-      <c r="X24" s="192"/>
-      <c r="Y24" s="192"/>
-      <c r="Z24" s="192"/>
-      <c r="AA24" s="192"/>
-      <c r="AB24" s="192"/>
-      <c r="AC24" s="192"/>
-      <c r="AD24" s="192"/>
-      <c r="AE24" s="192"/>
-      <c r="AF24" s="192"/>
-      <c r="AG24" s="192"/>
-      <c r="AH24" s="192"/>
-      <c r="AI24" s="192"/>
-      <c r="AJ24" s="192"/>
-      <c r="AK24" s="192"/>
-      <c r="AL24" s="192"/>
-      <c r="AM24" s="192"/>
-      <c r="AN24" s="192"/>
-      <c r="AO24" s="196"/>
+      <c r="A24" s="192"/>
+      <c r="B24" s="192"/>
+      <c r="C24" s="193"/>
+      <c r="D24" s="194"/>
+      <c r="E24" s="194"/>
+      <c r="F24" s="194"/>
+      <c r="G24" s="194"/>
+      <c r="H24" s="194"/>
+      <c r="I24" s="194"/>
+      <c r="J24" s="194"/>
+      <c r="K24" s="192"/>
+      <c r="L24" s="192"/>
+      <c r="M24" s="192"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="192"/>
+      <c r="P24" s="192"/>
+      <c r="Q24" s="193"/>
+      <c r="R24" s="194"/>
+      <c r="S24" s="194"/>
+      <c r="T24" s="194"/>
+      <c r="U24" s="194"/>
+      <c r="V24" s="194"/>
+      <c r="W24" s="194"/>
+      <c r="X24" s="194"/>
+      <c r="Y24" s="194"/>
+      <c r="Z24" s="194"/>
+      <c r="AA24" s="194"/>
+      <c r="AB24" s="194"/>
+      <c r="AC24" s="194"/>
+      <c r="AD24" s="194"/>
+      <c r="AE24" s="194"/>
+      <c r="AF24" s="194"/>
+      <c r="AG24" s="194"/>
+      <c r="AH24" s="194"/>
+      <c r="AI24" s="194"/>
+      <c r="AJ24" s="194"/>
+      <c r="AK24" s="194"/>
+      <c r="AL24" s="194"/>
+      <c r="AM24" s="194"/>
+      <c r="AN24" s="194"/>
+      <c r="AO24" s="198"/>
     </row>
     <row r="25" customHeight="1" spans="1:41">
-      <c r="A25" s="190"/>
-      <c r="B25" s="190"/>
-      <c r="C25" s="191"/>
-      <c r="D25" s="192"/>
-      <c r="E25" s="192"/>
-      <c r="F25" s="192"/>
-      <c r="G25" s="192"/>
-      <c r="H25" s="192"/>
-      <c r="I25" s="192"/>
-      <c r="J25" s="192"/>
-      <c r="K25" s="190"/>
-      <c r="L25" s="190"/>
-      <c r="M25" s="190"/>
-      <c r="N25" s="190"/>
-      <c r="O25" s="190"/>
-      <c r="P25" s="190"/>
-      <c r="Q25" s="191"/>
-      <c r="R25" s="192"/>
-      <c r="S25" s="192"/>
-      <c r="T25" s="192"/>
-      <c r="U25" s="192"/>
-      <c r="V25" s="192"/>
-      <c r="W25" s="192"/>
-      <c r="X25" s="192"/>
-      <c r="Y25" s="192"/>
-      <c r="Z25" s="192"/>
-      <c r="AA25" s="192"/>
-      <c r="AB25" s="192"/>
-      <c r="AC25" s="192"/>
-      <c r="AD25" s="192"/>
-      <c r="AE25" s="192"/>
-      <c r="AF25" s="192"/>
-      <c r="AG25" s="192"/>
-      <c r="AH25" s="192"/>
-      <c r="AI25" s="192"/>
-      <c r="AJ25" s="192"/>
-      <c r="AK25" s="192"/>
-      <c r="AL25" s="192"/>
-      <c r="AM25" s="192"/>
-      <c r="AN25" s="192"/>
-      <c r="AO25" s="196"/>
+      <c r="A25" s="192"/>
+      <c r="B25" s="192"/>
+      <c r="C25" s="193"/>
+      <c r="D25" s="194"/>
+      <c r="E25" s="194"/>
+      <c r="F25" s="194"/>
+      <c r="G25" s="194"/>
+      <c r="H25" s="194"/>
+      <c r="I25" s="194"/>
+      <c r="J25" s="194"/>
+      <c r="K25" s="192"/>
+      <c r="L25" s="192"/>
+      <c r="M25" s="192"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="192"/>
+      <c r="P25" s="192"/>
+      <c r="Q25" s="193"/>
+      <c r="R25" s="194"/>
+      <c r="S25" s="194"/>
+      <c r="T25" s="194"/>
+      <c r="U25" s="194"/>
+      <c r="V25" s="194"/>
+      <c r="W25" s="194"/>
+      <c r="X25" s="194"/>
+      <c r="Y25" s="194"/>
+      <c r="Z25" s="194"/>
+      <c r="AA25" s="194"/>
+      <c r="AB25" s="194"/>
+      <c r="AC25" s="194"/>
+      <c r="AD25" s="194"/>
+      <c r="AE25" s="194"/>
+      <c r="AF25" s="194"/>
+      <c r="AG25" s="194"/>
+      <c r="AH25" s="194"/>
+      <c r="AI25" s="194"/>
+      <c r="AJ25" s="194"/>
+      <c r="AK25" s="194"/>
+      <c r="AL25" s="194"/>
+      <c r="AM25" s="194"/>
+      <c r="AN25" s="194"/>
+      <c r="AO25" s="198"/>
     </row>
     <row r="26" customHeight="1" spans="1:41">
-      <c r="A26" s="190"/>
-      <c r="B26" s="190"/>
-      <c r="C26" s="191"/>
-      <c r="D26" s="192"/>
-      <c r="E26" s="192"/>
-      <c r="F26" s="192"/>
-      <c r="G26" s="192"/>
-      <c r="H26" s="192"/>
-      <c r="I26" s="192"/>
-      <c r="J26" s="192"/>
-      <c r="K26" s="190"/>
-      <c r="L26" s="190"/>
-      <c r="M26" s="190"/>
-      <c r="N26" s="190"/>
-      <c r="O26" s="190"/>
-      <c r="P26" s="190"/>
-      <c r="Q26" s="191"/>
-      <c r="R26" s="192"/>
-      <c r="S26" s="192"/>
-      <c r="T26" s="192"/>
-      <c r="U26" s="192"/>
-      <c r="V26" s="192"/>
-      <c r="W26" s="192"/>
-      <c r="X26" s="192"/>
-      <c r="Y26" s="192"/>
-      <c r="Z26" s="192"/>
-      <c r="AA26" s="192"/>
-      <c r="AB26" s="192"/>
-      <c r="AC26" s="192"/>
-      <c r="AD26" s="192"/>
-      <c r="AE26" s="192"/>
-      <c r="AF26" s="192"/>
-      <c r="AG26" s="192"/>
-      <c r="AH26" s="192"/>
-      <c r="AI26" s="192"/>
-      <c r="AJ26" s="192"/>
-      <c r="AK26" s="192"/>
-      <c r="AL26" s="192"/>
-      <c r="AM26" s="192"/>
-      <c r="AN26" s="192"/>
-      <c r="AO26" s="196"/>
+      <c r="A26" s="192"/>
+      <c r="B26" s="192"/>
+      <c r="C26" s="193"/>
+      <c r="D26" s="194"/>
+      <c r="E26" s="194"/>
+      <c r="F26" s="194"/>
+      <c r="G26" s="194"/>
+      <c r="H26" s="194"/>
+      <c r="I26" s="194"/>
+      <c r="J26" s="194"/>
+      <c r="K26" s="192"/>
+      <c r="L26" s="192"/>
+      <c r="M26" s="192"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="192"/>
+      <c r="P26" s="192"/>
+      <c r="Q26" s="193"/>
+      <c r="R26" s="194"/>
+      <c r="S26" s="194"/>
+      <c r="T26" s="194"/>
+      <c r="U26" s="194"/>
+      <c r="V26" s="194"/>
+      <c r="W26" s="194"/>
+      <c r="X26" s="194"/>
+      <c r="Y26" s="194"/>
+      <c r="Z26" s="194"/>
+      <c r="AA26" s="194"/>
+      <c r="AB26" s="194"/>
+      <c r="AC26" s="194"/>
+      <c r="AD26" s="194"/>
+      <c r="AE26" s="194"/>
+      <c r="AF26" s="194"/>
+      <c r="AG26" s="194"/>
+      <c r="AH26" s="194"/>
+      <c r="AI26" s="194"/>
+      <c r="AJ26" s="194"/>
+      <c r="AK26" s="194"/>
+      <c r="AL26" s="194"/>
+      <c r="AM26" s="194"/>
+      <c r="AN26" s="194"/>
+      <c r="AO26" s="198"/>
     </row>
     <row r="27" customHeight="1" spans="1:41">
-      <c r="A27" s="190"/>
-      <c r="B27" s="190"/>
-      <c r="C27" s="191"/>
-      <c r="D27" s="192"/>
-      <c r="E27" s="192"/>
-      <c r="F27" s="192"/>
-      <c r="G27" s="192"/>
-      <c r="H27" s="192"/>
-      <c r="I27" s="192"/>
-      <c r="J27" s="192"/>
-      <c r="K27" s="190"/>
-      <c r="L27" s="190"/>
-      <c r="M27" s="190"/>
-      <c r="N27" s="190"/>
-      <c r="O27" s="190"/>
-      <c r="P27" s="190"/>
-      <c r="Q27" s="191"/>
-      <c r="R27" s="192"/>
-      <c r="S27" s="192"/>
-      <c r="T27" s="192"/>
-      <c r="U27" s="192"/>
-      <c r="V27" s="192"/>
-      <c r="W27" s="192"/>
-      <c r="X27" s="192"/>
-      <c r="Y27" s="192"/>
-      <c r="Z27" s="192"/>
-      <c r="AA27" s="192"/>
-      <c r="AB27" s="192"/>
-      <c r="AC27" s="192"/>
-      <c r="AD27" s="192"/>
-      <c r="AE27" s="192"/>
-      <c r="AF27" s="192"/>
-      <c r="AG27" s="192"/>
-      <c r="AH27" s="192"/>
-      <c r="AI27" s="192"/>
-      <c r="AJ27" s="192"/>
-      <c r="AK27" s="192"/>
-      <c r="AL27" s="192"/>
-      <c r="AM27" s="192"/>
-      <c r="AN27" s="192"/>
-      <c r="AO27" s="196"/>
+      <c r="A27" s="192"/>
+      <c r="B27" s="192"/>
+      <c r="C27" s="193"/>
+      <c r="D27" s="194"/>
+      <c r="E27" s="194"/>
+      <c r="F27" s="194"/>
+      <c r="G27" s="194"/>
+      <c r="H27" s="194"/>
+      <c r="I27" s="194"/>
+      <c r="J27" s="194"/>
+      <c r="K27" s="192"/>
+      <c r="L27" s="192"/>
+      <c r="M27" s="192"/>
+      <c r="N27" s="192"/>
+      <c r="O27" s="192"/>
+      <c r="P27" s="192"/>
+      <c r="Q27" s="193"/>
+      <c r="R27" s="194"/>
+      <c r="S27" s="194"/>
+      <c r="T27" s="194"/>
+      <c r="U27" s="194"/>
+      <c r="V27" s="194"/>
+      <c r="W27" s="194"/>
+      <c r="X27" s="194"/>
+      <c r="Y27" s="194"/>
+      <c r="Z27" s="194"/>
+      <c r="AA27" s="194"/>
+      <c r="AB27" s="194"/>
+      <c r="AC27" s="194"/>
+      <c r="AD27" s="194"/>
+      <c r="AE27" s="194"/>
+      <c r="AF27" s="194"/>
+      <c r="AG27" s="194"/>
+      <c r="AH27" s="194"/>
+      <c r="AI27" s="194"/>
+      <c r="AJ27" s="194"/>
+      <c r="AK27" s="194"/>
+      <c r="AL27" s="194"/>
+      <c r="AM27" s="194"/>
+      <c r="AN27" s="194"/>
+      <c r="AO27" s="198"/>
     </row>
     <row r="28" customHeight="1" spans="1:41">
-      <c r="A28" s="190"/>
-      <c r="B28" s="190"/>
-      <c r="C28" s="191"/>
-      <c r="D28" s="192"/>
-      <c r="E28" s="192"/>
-      <c r="F28" s="192"/>
-      <c r="G28" s="192"/>
-      <c r="H28" s="192"/>
-      <c r="I28" s="192"/>
-      <c r="J28" s="192"/>
-      <c r="K28" s="190"/>
-      <c r="L28" s="190"/>
-      <c r="M28" s="190"/>
-      <c r="N28" s="190"/>
-      <c r="O28" s="190"/>
-      <c r="P28" s="190"/>
-      <c r="Q28" s="191"/>
-      <c r="R28" s="192"/>
-      <c r="S28" s="192"/>
-      <c r="T28" s="192"/>
-      <c r="U28" s="192"/>
-      <c r="V28" s="192"/>
-      <c r="W28" s="192"/>
-      <c r="X28" s="192"/>
-      <c r="Y28" s="192"/>
-      <c r="Z28" s="192"/>
-      <c r="AA28" s="192"/>
-      <c r="AB28" s="192"/>
-      <c r="AC28" s="192"/>
-      <c r="AD28" s="192"/>
-      <c r="AE28" s="192"/>
-      <c r="AF28" s="192"/>
-      <c r="AG28" s="192"/>
-      <c r="AH28" s="192"/>
-      <c r="AI28" s="192"/>
-      <c r="AJ28" s="192"/>
-      <c r="AK28" s="192"/>
-      <c r="AL28" s="192"/>
-      <c r="AM28" s="192"/>
-      <c r="AN28" s="192"/>
-      <c r="AO28" s="196"/>
+      <c r="A28" s="192"/>
+      <c r="B28" s="192"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="194"/>
+      <c r="E28" s="194"/>
+      <c r="F28" s="194"/>
+      <c r="G28" s="194"/>
+      <c r="H28" s="194"/>
+      <c r="I28" s="194"/>
+      <c r="J28" s="194"/>
+      <c r="K28" s="192"/>
+      <c r="L28" s="192"/>
+      <c r="M28" s="192"/>
+      <c r="N28" s="192"/>
+      <c r="O28" s="192"/>
+      <c r="P28" s="192"/>
+      <c r="Q28" s="193"/>
+      <c r="R28" s="194"/>
+      <c r="S28" s="194"/>
+      <c r="T28" s="194"/>
+      <c r="U28" s="194"/>
+      <c r="V28" s="194"/>
+      <c r="W28" s="194"/>
+      <c r="X28" s="194"/>
+      <c r="Y28" s="194"/>
+      <c r="Z28" s="194"/>
+      <c r="AA28" s="194"/>
+      <c r="AB28" s="194"/>
+      <c r="AC28" s="194"/>
+      <c r="AD28" s="194"/>
+      <c r="AE28" s="194"/>
+      <c r="AF28" s="194"/>
+      <c r="AG28" s="194"/>
+      <c r="AH28" s="194"/>
+      <c r="AI28" s="194"/>
+      <c r="AJ28" s="194"/>
+      <c r="AK28" s="194"/>
+      <c r="AL28" s="194"/>
+      <c r="AM28" s="194"/>
+      <c r="AN28" s="194"/>
+      <c r="AO28" s="198"/>
     </row>
     <row r="29" customHeight="1" spans="1:41">
-      <c r="A29" s="190"/>
-      <c r="B29" s="190"/>
-      <c r="C29" s="191"/>
-      <c r="D29" s="192"/>
-      <c r="E29" s="192"/>
-      <c r="F29" s="192"/>
-      <c r="G29" s="192"/>
-      <c r="H29" s="192"/>
-      <c r="I29" s="192"/>
-      <c r="J29" s="192"/>
-      <c r="K29" s="190"/>
-      <c r="L29" s="190"/>
-      <c r="M29" s="190"/>
-      <c r="N29" s="190"/>
-      <c r="O29" s="190"/>
-      <c r="P29" s="190"/>
-      <c r="Q29" s="191"/>
-      <c r="R29" s="192"/>
-      <c r="S29" s="192"/>
-      <c r="T29" s="192"/>
-      <c r="U29" s="192"/>
-      <c r="V29" s="192"/>
-      <c r="W29" s="192"/>
-      <c r="X29" s="192"/>
-      <c r="Y29" s="192"/>
-      <c r="Z29" s="192"/>
-      <c r="AA29" s="192"/>
-      <c r="AB29" s="192"/>
-      <c r="AC29" s="192"/>
-      <c r="AD29" s="192"/>
-      <c r="AE29" s="192"/>
-      <c r="AF29" s="192"/>
-      <c r="AG29" s="192"/>
-      <c r="AH29" s="192"/>
-      <c r="AI29" s="192"/>
-      <c r="AJ29" s="192"/>
-      <c r="AK29" s="192"/>
-      <c r="AL29" s="192"/>
-      <c r="AM29" s="192"/>
-      <c r="AN29" s="192"/>
-      <c r="AO29" s="196"/>
+      <c r="A29" s="192"/>
+      <c r="B29" s="192"/>
+      <c r="C29" s="193"/>
+      <c r="D29" s="194"/>
+      <c r="E29" s="194"/>
+      <c r="F29" s="194"/>
+      <c r="G29" s="194"/>
+      <c r="H29" s="194"/>
+      <c r="I29" s="194"/>
+      <c r="J29" s="194"/>
+      <c r="K29" s="192"/>
+      <c r="L29" s="192"/>
+      <c r="M29" s="192"/>
+      <c r="N29" s="192"/>
+      <c r="O29" s="192"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="193"/>
+      <c r="R29" s="194"/>
+      <c r="S29" s="194"/>
+      <c r="T29" s="194"/>
+      <c r="U29" s="194"/>
+      <c r="V29" s="194"/>
+      <c r="W29" s="194"/>
+      <c r="X29" s="194"/>
+      <c r="Y29" s="194"/>
+      <c r="Z29" s="194"/>
+      <c r="AA29" s="194"/>
+      <c r="AB29" s="194"/>
+      <c r="AC29" s="194"/>
+      <c r="AD29" s="194"/>
+      <c r="AE29" s="194"/>
+      <c r="AF29" s="194"/>
+      <c r="AG29" s="194"/>
+      <c r="AH29" s="194"/>
+      <c r="AI29" s="194"/>
+      <c r="AJ29" s="194"/>
+      <c r="AK29" s="194"/>
+      <c r="AL29" s="194"/>
+      <c r="AM29" s="194"/>
+      <c r="AN29" s="194"/>
+      <c r="AO29" s="198"/>
     </row>
     <row r="30" customHeight="1" spans="1:41">
-      <c r="A30" s="190"/>
-      <c r="B30" s="190"/>
-      <c r="C30" s="191"/>
-      <c r="D30" s="192"/>
-      <c r="E30" s="192"/>
-      <c r="F30" s="192"/>
-      <c r="G30" s="192"/>
-      <c r="H30" s="192"/>
-      <c r="I30" s="192"/>
-      <c r="J30" s="192"/>
-      <c r="K30" s="190"/>
-      <c r="L30" s="190"/>
-      <c r="M30" s="190"/>
-      <c r="N30" s="190"/>
-      <c r="O30" s="190"/>
-      <c r="P30" s="190"/>
-      <c r="Q30" s="191"/>
-      <c r="R30" s="192"/>
-      <c r="S30" s="192"/>
-      <c r="T30" s="192"/>
-      <c r="U30" s="192"/>
-      <c r="V30" s="192"/>
-      <c r="W30" s="192"/>
-      <c r="X30" s="192"/>
-      <c r="Y30" s="192"/>
-      <c r="Z30" s="192"/>
-      <c r="AA30" s="192"/>
-      <c r="AB30" s="192"/>
-      <c r="AC30" s="192"/>
-      <c r="AD30" s="192"/>
-      <c r="AE30" s="192"/>
-      <c r="AF30" s="192"/>
-      <c r="AG30" s="192"/>
-      <c r="AH30" s="192"/>
-      <c r="AI30" s="192"/>
-      <c r="AJ30" s="192"/>
-      <c r="AK30" s="192"/>
-      <c r="AL30" s="192"/>
-      <c r="AM30" s="192"/>
-      <c r="AN30" s="192"/>
-      <c r="AO30" s="196"/>
+      <c r="A30" s="192"/>
+      <c r="B30" s="192"/>
+      <c r="C30" s="193"/>
+      <c r="D30" s="194"/>
+      <c r="E30" s="194"/>
+      <c r="F30" s="194"/>
+      <c r="G30" s="194"/>
+      <c r="H30" s="194"/>
+      <c r="I30" s="194"/>
+      <c r="J30" s="194"/>
+      <c r="K30" s="192"/>
+      <c r="L30" s="192"/>
+      <c r="M30" s="192"/>
+      <c r="N30" s="192"/>
+      <c r="O30" s="192"/>
+      <c r="P30" s="192"/>
+      <c r="Q30" s="193"/>
+      <c r="R30" s="194"/>
+      <c r="S30" s="194"/>
+      <c r="T30" s="194"/>
+      <c r="U30" s="194"/>
+      <c r="V30" s="194"/>
+      <c r="W30" s="194"/>
+      <c r="X30" s="194"/>
+      <c r="Y30" s="194"/>
+      <c r="Z30" s="194"/>
+      <c r="AA30" s="194"/>
+      <c r="AB30" s="194"/>
+      <c r="AC30" s="194"/>
+      <c r="AD30" s="194"/>
+      <c r="AE30" s="194"/>
+      <c r="AF30" s="194"/>
+      <c r="AG30" s="194"/>
+      <c r="AH30" s="194"/>
+      <c r="AI30" s="194"/>
+      <c r="AJ30" s="194"/>
+      <c r="AK30" s="194"/>
+      <c r="AL30" s="194"/>
+      <c r="AM30" s="194"/>
+      <c r="AN30" s="194"/>
+      <c r="AO30" s="198"/>
     </row>
     <row r="31" customHeight="1" spans="1:41">
-      <c r="A31" s="190"/>
-      <c r="B31" s="190"/>
-      <c r="C31" s="191"/>
-      <c r="D31" s="192"/>
-      <c r="E31" s="192"/>
-      <c r="F31" s="192"/>
-      <c r="G31" s="192"/>
-      <c r="H31" s="192"/>
-      <c r="I31" s="192"/>
-      <c r="J31" s="192"/>
-      <c r="K31" s="190"/>
-      <c r="L31" s="190"/>
-      <c r="M31" s="190"/>
-      <c r="N31" s="190"/>
-      <c r="O31" s="190"/>
-      <c r="P31" s="190"/>
-      <c r="Q31" s="191"/>
-      <c r="R31" s="192"/>
-      <c r="S31" s="192"/>
-      <c r="T31" s="192"/>
-      <c r="U31" s="192"/>
-      <c r="V31" s="192"/>
-      <c r="W31" s="192"/>
-      <c r="X31" s="192"/>
-      <c r="Y31" s="192"/>
-      <c r="Z31" s="192"/>
-      <c r="AA31" s="192"/>
-      <c r="AB31" s="192"/>
-      <c r="AC31" s="192"/>
-      <c r="AD31" s="192"/>
-      <c r="AE31" s="192"/>
-      <c r="AF31" s="192"/>
-      <c r="AG31" s="192"/>
-      <c r="AH31" s="192"/>
-      <c r="AI31" s="192"/>
-      <c r="AJ31" s="192"/>
-      <c r="AK31" s="192"/>
-      <c r="AL31" s="192"/>
-      <c r="AM31" s="192"/>
-      <c r="AN31" s="192"/>
-      <c r="AO31" s="196"/>
+      <c r="A31" s="192"/>
+      <c r="B31" s="192"/>
+      <c r="C31" s="193"/>
+      <c r="D31" s="194"/>
+      <c r="E31" s="194"/>
+      <c r="F31" s="194"/>
+      <c r="G31" s="194"/>
+      <c r="H31" s="194"/>
+      <c r="I31" s="194"/>
+      <c r="J31" s="194"/>
+      <c r="K31" s="192"/>
+      <c r="L31" s="192"/>
+      <c r="M31" s="192"/>
+      <c r="N31" s="192"/>
+      <c r="O31" s="192"/>
+      <c r="P31" s="192"/>
+      <c r="Q31" s="193"/>
+      <c r="R31" s="194"/>
+      <c r="S31" s="194"/>
+      <c r="T31" s="194"/>
+      <c r="U31" s="194"/>
+      <c r="V31" s="194"/>
+      <c r="W31" s="194"/>
+      <c r="X31" s="194"/>
+      <c r="Y31" s="194"/>
+      <c r="Z31" s="194"/>
+      <c r="AA31" s="194"/>
+      <c r="AB31" s="194"/>
+      <c r="AC31" s="194"/>
+      <c r="AD31" s="194"/>
+      <c r="AE31" s="194"/>
+      <c r="AF31" s="194"/>
+      <c r="AG31" s="194"/>
+      <c r="AH31" s="194"/>
+      <c r="AI31" s="194"/>
+      <c r="AJ31" s="194"/>
+      <c r="AK31" s="194"/>
+      <c r="AL31" s="194"/>
+      <c r="AM31" s="194"/>
+      <c r="AN31" s="194"/>
+      <c r="AO31" s="198"/>
     </row>
     <row r="32" customHeight="1" spans="1:41">
-      <c r="A32" s="190"/>
-      <c r="B32" s="190"/>
-      <c r="C32" s="191"/>
-      <c r="D32" s="192"/>
-      <c r="E32" s="192"/>
-      <c r="F32" s="192"/>
-      <c r="G32" s="192"/>
-      <c r="H32" s="192"/>
-      <c r="I32" s="192"/>
-      <c r="J32" s="192"/>
-      <c r="K32" s="190"/>
-      <c r="L32" s="190"/>
-      <c r="M32" s="190"/>
-      <c r="N32" s="190"/>
-      <c r="O32" s="190"/>
-      <c r="P32" s="190"/>
-      <c r="Q32" s="191"/>
-      <c r="R32" s="192"/>
-      <c r="S32" s="192"/>
-      <c r="T32" s="192"/>
-      <c r="U32" s="192"/>
-      <c r="V32" s="192"/>
-      <c r="W32" s="192"/>
-      <c r="X32" s="192"/>
-      <c r="Y32" s="192"/>
-      <c r="Z32" s="192"/>
-      <c r="AA32" s="192"/>
-      <c r="AB32" s="192"/>
-      <c r="AC32" s="192"/>
-      <c r="AD32" s="192"/>
-      <c r="AE32" s="192"/>
-      <c r="AF32" s="192"/>
-      <c r="AG32" s="192"/>
-      <c r="AH32" s="192"/>
-      <c r="AI32" s="192"/>
-      <c r="AJ32" s="192"/>
-      <c r="AK32" s="192"/>
-      <c r="AL32" s="192"/>
-      <c r="AM32" s="192"/>
-      <c r="AN32" s="192"/>
-      <c r="AO32" s="196"/>
+      <c r="A32" s="192"/>
+      <c r="B32" s="192"/>
+      <c r="C32" s="193"/>
+      <c r="D32" s="194"/>
+      <c r="E32" s="194"/>
+      <c r="F32" s="194"/>
+      <c r="G32" s="194"/>
+      <c r="H32" s="194"/>
+      <c r="I32" s="194"/>
+      <c r="J32" s="194"/>
+      <c r="K32" s="192"/>
+      <c r="L32" s="192"/>
+      <c r="M32" s="192"/>
+      <c r="N32" s="192"/>
+      <c r="O32" s="192"/>
+      <c r="P32" s="192"/>
+      <c r="Q32" s="193"/>
+      <c r="R32" s="194"/>
+      <c r="S32" s="194"/>
+      <c r="T32" s="194"/>
+      <c r="U32" s="194"/>
+      <c r="V32" s="194"/>
+      <c r="W32" s="194"/>
+      <c r="X32" s="194"/>
+      <c r="Y32" s="194"/>
+      <c r="Z32" s="194"/>
+      <c r="AA32" s="194"/>
+      <c r="AB32" s="194"/>
+      <c r="AC32" s="194"/>
+      <c r="AD32" s="194"/>
+      <c r="AE32" s="194"/>
+      <c r="AF32" s="194"/>
+      <c r="AG32" s="194"/>
+      <c r="AH32" s="194"/>
+      <c r="AI32" s="194"/>
+      <c r="AJ32" s="194"/>
+      <c r="AK32" s="194"/>
+      <c r="AL32" s="194"/>
+      <c r="AM32" s="194"/>
+      <c r="AN32" s="194"/>
+      <c r="AO32" s="198"/>
     </row>
     <row r="33" customHeight="1" spans="1:41">
       <c r="A33" s="30"/>
@@ -8728,18 +8749,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XEJ15"/>
+  <dimension ref="A1:XEJ11"/>
   <sheetFormatPr defaultColWidth="3.71111111111111" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.88888888888889" style="1"/>
+    <col min="1" max="1" width="4.28148148148148" style="1" customWidth="1"/>
     <col min="2" max="4" width="3.71111111111111" style="1"/>
-    <col min="5" max="5" width="20.3111111111111" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.4592592592593" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5407407407407" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.0296296296296" style="1" customWidth="1"/>
     <col min="7" max="7" width="25.8740740740741" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.437037037037" style="1" customWidth="1"/>
-    <col min="9" max="9" width="23.8074074074074" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.8" style="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5777777777778" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.6222222222222" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5851851851852" style="1" customWidth="1"/>
+    <col min="10" max="10" width="21.4222222222222" style="1" customWidth="1"/>
+    <col min="11" max="11" width="30.7851851851852" style="1" customWidth="1"/>
     <col min="12" max="16357" width="3.71111111111111" style="1"/>
   </cols>
   <sheetData>
@@ -8760,13 +8781,13 @@
       <c r="H1" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="179" t="s">
+      <c r="I1" s="180" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="155" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="180">
+      <c r="K1" s="181">
         <v>45735</v>
       </c>
     </row>
@@ -8783,9 +8804,9 @@
         <v>15</v>
       </c>
       <c r="H2" s="158"/>
-      <c r="I2" s="181"/>
+      <c r="I2" s="182"/>
       <c r="J2" s="158"/>
-      <c r="K2" s="182"/>
+      <c r="K2" s="183"/>
     </row>
     <row r="3" customHeight="1" spans="1:11">
       <c r="A3" s="156"/>
@@ -8802,11 +8823,11 @@
       <c r="H3" s="155" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="179"/>
+      <c r="I3" s="180"/>
       <c r="J3" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="179"/>
+      <c r="K3" s="180"/>
     </row>
     <row r="4" customHeight="1" spans="1:11">
       <c r="A4" s="159"/>
@@ -8821,9 +8842,9 @@
         <v>21</v>
       </c>
       <c r="H4" s="158"/>
-      <c r="I4" s="181"/>
+      <c r="I4" s="182"/>
       <c r="J4" s="158"/>
-      <c r="K4" s="181"/>
+      <c r="K4" s="182"/>
     </row>
     <row r="5" s="150" customFormat="1" customHeight="1" spans="1:16337">
       <c r="A5" s="152"/>
@@ -8837,7 +8858,7 @@
       <c r="I5" s="161"/>
       <c r="J5" s="161"/>
       <c r="K5" s="161"/>
-      <c r="XDI5" s="187"/>
+      <c r="XDI5" s="189"/>
     </row>
     <row r="6" s="150" customFormat="1" customHeight="1" spans="1:16364">
       <c r="A6" s="162" t="s">
@@ -8861,7 +8882,7 @@
       <c r="I6" s="162"/>
       <c r="J6" s="162"/>
       <c r="K6" s="162"/>
-      <c r="XEJ6" s="187"/>
+      <c r="XEJ6" s="189"/>
     </row>
     <row r="7" s="150" customFormat="1" customHeight="1" spans="1:16364">
       <c r="A7" s="167"/>
@@ -8880,12 +8901,12 @@
       <c r="H7" s="169" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="183"/>
+      <c r="I7" s="184"/>
       <c r="J7" s="169" t="s">
         <v>48</v>
       </c>
-      <c r="K7" s="183"/>
-      <c r="XEJ7" s="187"/>
+      <c r="K7" s="184"/>
+      <c r="XEJ7" s="189"/>
     </row>
     <row r="8" s="150" customFormat="1" customHeight="1" spans="1:16364">
       <c r="A8" s="170">
@@ -8894,161 +8915,105 @@
       <c r="B8" s="171" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="171"/>
-      <c r="D8" s="171"/>
-      <c r="E8" s="171"/>
-      <c r="F8" s="172" t="s">
+      <c r="C8" s="172"/>
+      <c r="D8" s="172"/>
+      <c r="E8" s="172"/>
+      <c r="F8" s="173" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="172" t="s">
+      <c r="G8" s="173" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="173" t="s">
+      <c r="H8" s="174" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="184"/>
-      <c r="J8" s="173" t="s">
+      <c r="I8" s="185"/>
+      <c r="J8" s="174" t="s">
         <v>37</v>
       </c>
-      <c r="K8" s="184"/>
-      <c r="XEJ8" s="187"/>
-    </row>
-    <row r="9" s="150" customFormat="1" customHeight="1" spans="1:16364">
-      <c r="A9" s="170">
+      <c r="K8" s="185"/>
+      <c r="XEJ8" s="189"/>
+    </row>
+    <row r="9" s="150" customFormat="1" ht="42" customHeight="1" spans="1:16364">
+      <c r="A9" s="173">
         <v>2</v>
       </c>
       <c r="B9" s="171" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172" t="s">
+      <c r="C9" s="172"/>
+      <c r="D9" s="172"/>
+      <c r="E9" s="172"/>
+      <c r="F9" s="173" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="172" t="s">
+      <c r="G9" s="173" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="174" t="s">
+      <c r="H9" s="175" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="185"/>
-      <c r="J9" s="173" t="s">
+      <c r="I9" s="186"/>
+      <c r="J9" s="174" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="184"/>
-      <c r="XEJ9" s="187"/>
+      <c r="K9" s="185"/>
+      <c r="XEJ9" s="189"/>
     </row>
     <row r="10" s="150" customFormat="1" customHeight="1" spans="1:16364">
-      <c r="A10" s="170">
+      <c r="A10" s="173">
         <v>3</v>
       </c>
       <c r="B10" s="171" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="171"/>
-      <c r="D10" s="171"/>
-      <c r="E10" s="171"/>
-      <c r="F10" s="172" t="s">
+      <c r="C10" s="172"/>
+      <c r="D10" s="172"/>
+      <c r="E10" s="172"/>
+      <c r="F10" s="173" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="172" t="s">
+      <c r="G10" s="173" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="173" t="s">
+      <c r="H10" s="174" t="s">
         <v>37</v>
       </c>
-      <c r="I10" s="184"/>
-      <c r="J10" s="173" t="s">
+      <c r="I10" s="185"/>
+      <c r="J10" s="174" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="185"/>
+      <c r="XEJ10" s="189"/>
+    </row>
+    <row r="11" s="150" customFormat="1" ht="22" customHeight="1" spans="1:16364">
+      <c r="A11" s="176">
+        <v>4</v>
+      </c>
+      <c r="B11" s="177" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="184"/>
-      <c r="XEJ10" s="187"/>
-    </row>
-    <row r="11" s="150" customFormat="1" customHeight="1" spans="1:16364">
-      <c r="A11" s="170">
-        <v>4</v>
-      </c>
-      <c r="B11" s="171" t="s">
+      <c r="C11" s="178"/>
+      <c r="D11" s="178"/>
+      <c r="E11" s="178"/>
+      <c r="F11" s="176" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="171"/>
-      <c r="D11" s="171"/>
-      <c r="E11" s="171"/>
-      <c r="F11" s="172" t="s">
+      <c r="G11" s="176" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="172" t="s">
+      <c r="H11" s="179" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="177"/>
+      <c r="J11" s="187" t="s">
         <v>60</v>
       </c>
-      <c r="H11" s="174" t="s">
-        <v>37</v>
-      </c>
-      <c r="I11" s="185"/>
-      <c r="J11" s="174" t="s">
-        <v>61</v>
-      </c>
-      <c r="K11" s="185"/>
-      <c r="XEJ11" s="187"/>
-    </row>
-    <row r="12" s="150" customFormat="1" customHeight="1" spans="1:16364">
-      <c r="A12" s="170"/>
-      <c r="B12" s="171"/>
-      <c r="C12" s="171"/>
-      <c r="D12" s="171"/>
-      <c r="E12" s="171"/>
-      <c r="F12" s="172"/>
-      <c r="G12" s="172"/>
-      <c r="H12" s="174"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="174"/>
-      <c r="K12" s="185"/>
-      <c r="XEJ12" s="187"/>
-    </row>
-    <row r="13" s="150" customFormat="1" customHeight="1" spans="1:16364">
-      <c r="A13" s="170"/>
-      <c r="B13" s="171"/>
-      <c r="C13" s="171"/>
-      <c r="D13" s="171"/>
-      <c r="E13" s="171"/>
-      <c r="F13" s="172"/>
-      <c r="G13" s="172"/>
-      <c r="H13" s="174"/>
-      <c r="I13" s="185"/>
-      <c r="J13" s="174"/>
-      <c r="K13" s="185"/>
-      <c r="XEJ13" s="187"/>
-    </row>
-    <row r="14" s="150" customFormat="1" customHeight="1" spans="1:16364">
-      <c r="A14" s="170"/>
-      <c r="B14" s="171"/>
-      <c r="C14" s="171"/>
-      <c r="D14" s="171"/>
-      <c r="E14" s="171"/>
-      <c r="F14" s="172"/>
-      <c r="G14" s="172"/>
-      <c r="H14" s="174"/>
-      <c r="I14" s="185"/>
-      <c r="J14" s="174"/>
-      <c r="K14" s="185"/>
-      <c r="XEJ14" s="187"/>
-    </row>
-    <row r="15" s="150" customFormat="1" customHeight="1" spans="1:16364">
-      <c r="A15" s="175"/>
-      <c r="B15" s="176"/>
-      <c r="C15" s="176"/>
-      <c r="D15" s="176"/>
-      <c r="E15" s="176"/>
-      <c r="F15" s="177"/>
-      <c r="G15" s="177"/>
-      <c r="H15" s="178"/>
-      <c r="I15" s="186"/>
-      <c r="J15" s="178"/>
-      <c r="K15" s="186"/>
-      <c r="XEJ15" s="187"/>
+      <c r="K11" s="188"/>
+      <c r="XEJ11" s="189"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="27">
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="G6:K6"/>
     <mergeCell ref="B7:E7"/>
@@ -9066,18 +9031,6 @@
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="J11:K11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="H3:H4"/>
@@ -9090,15 +9043,18 @@
     <mergeCell ref="A1:E4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="46" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="45" orientation="portrait"/>
   <headerFooter/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="12" max="16" man="1"/>
+  </colBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AL104"/>
+  <dimension ref="A1:AL73"/>
   <sheetFormatPr defaultColWidth="3.71111111111111" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="9" width="3.71111111111111" style="1"/>
@@ -9112,7 +9068,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:38">
       <c r="A1" s="92" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B1" s="93"/>
       <c r="C1" s="93"/>
@@ -9350,7 +9306,7 @@
     </row>
     <row r="6" customHeight="1" spans="1:38">
       <c r="A6" s="48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" s="49"/>
       <c r="C6" s="49"/>
@@ -9392,7 +9348,7 @@
     </row>
     <row r="7" customHeight="1" spans="1:38">
       <c r="A7" s="102" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B7" s="102"/>
       <c r="C7" s="102"/>
@@ -9435,7 +9391,7 @@
     <row r="8" customHeight="1" spans="1:38">
       <c r="A8" s="103"/>
       <c r="B8" s="87" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" s="87"/>
       <c r="D8" s="87"/>
@@ -9727,7 +9683,7 @@
       <c r="J15" s="104"/>
       <c r="K15" s="123"/>
       <c r="L15" s="124" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="M15" s="123"/>
       <c r="N15" s="123"/>
@@ -9889,7 +9845,7 @@
       <c r="J19" s="104"/>
       <c r="K19" s="123"/>
       <c r="L19" s="124" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="M19" s="123"/>
       <c r="N19" s="123"/>
@@ -10055,7 +10011,7 @@
       <c r="N23" s="125"/>
       <c r="O23" s="125"/>
       <c r="P23" s="126" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="Q23" s="125"/>
       <c r="R23" s="125"/>
@@ -10171,7 +10127,7 @@
       <c r="H26" s="108"/>
       <c r="I26" s="128"/>
       <c r="M26" s="129" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="X26" s="141"/>
       <c r="Y26" s="135"/>
@@ -10415,7 +10371,7 @@
     </row>
     <row r="43" customHeight="1" spans="1:38">
       <c r="A43" s="102" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B43" s="102"/>
       <c r="C43" s="102"/>
@@ -10458,7 +10414,7 @@
     <row r="44" customHeight="1" spans="1:38">
       <c r="A44" s="113"/>
       <c r="B44" s="87" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C44" s="113"/>
       <c r="D44" s="113"/>
@@ -10497,69 +10453,42 @@
       <c r="AK44" s="113"/>
       <c r="AL44" s="113"/>
     </row>
-    <row r="45" customHeight="1" spans="3:32">
-      <c r="C45" s="105"/>
-      <c r="D45" s="106"/>
-      <c r="E45" s="106"/>
-      <c r="F45" s="106"/>
-      <c r="G45" s="106"/>
-      <c r="H45" s="106"/>
-      <c r="I45" s="106"/>
-      <c r="J45" s="106"/>
-      <c r="K45" s="106"/>
-      <c r="L45" s="106"/>
-      <c r="M45" s="106"/>
-      <c r="N45" s="106"/>
-      <c r="O45" s="106"/>
-      <c r="P45" s="106"/>
-      <c r="Q45" s="106"/>
-      <c r="R45" s="106"/>
-      <c r="S45" s="106"/>
-      <c r="T45" s="106"/>
-      <c r="U45" s="106"/>
-      <c r="V45" s="106"/>
-      <c r="W45" s="134"/>
-      <c r="X45" s="134"/>
-      <c r="Y45" s="134"/>
-      <c r="Z45" s="134"/>
-      <c r="AA45" s="134"/>
-      <c r="AB45" s="134"/>
-      <c r="AC45" s="134"/>
-      <c r="AD45" s="134"/>
-      <c r="AE45" s="134"/>
-      <c r="AF45" s="144"/>
+    <row r="45" customHeight="1" spans="2:2">
+      <c r="B45" s="87" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="46" customHeight="1" spans="3:32">
-      <c r="C46" s="107"/>
-      <c r="D46" s="108"/>
-      <c r="E46" s="108"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="108"/>
-      <c r="H46" s="108"/>
-      <c r="I46" s="108"/>
-      <c r="J46" s="108"/>
-      <c r="K46" s="108"/>
-      <c r="L46" s="108"/>
-      <c r="M46" s="108"/>
-      <c r="N46" s="108"/>
-      <c r="O46" s="108"/>
-      <c r="P46" s="108"/>
-      <c r="Q46" s="108"/>
-      <c r="R46" s="108"/>
-      <c r="S46" s="108"/>
-      <c r="T46" s="108"/>
-      <c r="U46" s="108"/>
-      <c r="V46" s="108"/>
-      <c r="W46" s="135"/>
-      <c r="X46" s="135"/>
-      <c r="Y46" s="135"/>
-      <c r="Z46" s="135"/>
-      <c r="AA46" s="135"/>
-      <c r="AB46" s="135"/>
-      <c r="AC46" s="135"/>
-      <c r="AD46" s="135"/>
-      <c r="AE46" s="135"/>
-      <c r="AF46" s="145"/>
+      <c r="C46" s="105"/>
+      <c r="D46" s="106"/>
+      <c r="E46" s="106"/>
+      <c r="F46" s="106"/>
+      <c r="G46" s="106"/>
+      <c r="H46" s="106"/>
+      <c r="I46" s="106"/>
+      <c r="J46" s="106"/>
+      <c r="K46" s="106"/>
+      <c r="L46" s="106"/>
+      <c r="M46" s="106"/>
+      <c r="N46" s="106"/>
+      <c r="O46" s="106"/>
+      <c r="P46" s="106"/>
+      <c r="Q46" s="106"/>
+      <c r="R46" s="106"/>
+      <c r="S46" s="106"/>
+      <c r="T46" s="106"/>
+      <c r="U46" s="106"/>
+      <c r="V46" s="106"/>
+      <c r="W46" s="134"/>
+      <c r="X46" s="134"/>
+      <c r="Y46" s="134"/>
+      <c r="Z46" s="134"/>
+      <c r="AA46" s="134"/>
+      <c r="AB46" s="134"/>
+      <c r="AC46" s="134"/>
+      <c r="AD46" s="134"/>
+      <c r="AE46" s="134"/>
+      <c r="AF46" s="144"/>
     </row>
     <row r="47" customHeight="1" spans="3:32">
       <c r="C47" s="107"/>
@@ -10570,9 +10499,7 @@
       <c r="H47" s="108"/>
       <c r="I47" s="108"/>
       <c r="J47" s="108"/>
-      <c r="K47" s="132" t="s">
-        <v>71</v>
-      </c>
+      <c r="K47" s="108"/>
       <c r="L47" s="108"/>
       <c r="M47" s="108"/>
       <c r="N47" s="108"/>
@@ -10602,22 +10529,24 @@
       <c r="F48" s="108"/>
       <c r="G48" s="108"/>
       <c r="H48" s="108"/>
-      <c r="I48" s="120"/>
-      <c r="J48" s="121"/>
-      <c r="K48" s="121"/>
-      <c r="L48" s="121"/>
-      <c r="M48" s="121"/>
-      <c r="N48" s="121"/>
-      <c r="O48" s="121"/>
-      <c r="P48" s="121"/>
-      <c r="Q48" s="121"/>
-      <c r="R48" s="121"/>
-      <c r="S48" s="121"/>
-      <c r="T48" s="121"/>
-      <c r="U48" s="121"/>
-      <c r="V48" s="121"/>
-      <c r="W48" s="136"/>
-      <c r="X48" s="137"/>
+      <c r="I48" s="108"/>
+      <c r="J48" s="108"/>
+      <c r="K48" s="132" t="s">
+        <v>68</v>
+      </c>
+      <c r="L48" s="108"/>
+      <c r="M48" s="108"/>
+      <c r="N48" s="108"/>
+      <c r="O48" s="108"/>
+      <c r="P48" s="108"/>
+      <c r="Q48" s="108"/>
+      <c r="R48" s="108"/>
+      <c r="S48" s="108"/>
+      <c r="T48" s="108"/>
+      <c r="U48" s="108"/>
+      <c r="V48" s="108"/>
+      <c r="W48" s="135"/>
+      <c r="X48" s="135"/>
       <c r="Y48" s="135"/>
       <c r="Z48" s="135"/>
       <c r="AA48" s="135"/>
@@ -10634,22 +10563,22 @@
       <c r="F49" s="108"/>
       <c r="G49" s="108"/>
       <c r="H49" s="108"/>
-      <c r="I49" s="122"/>
-      <c r="J49" s="104"/>
-      <c r="K49" s="104"/>
-      <c r="L49" s="104"/>
-      <c r="M49" s="104"/>
-      <c r="N49" s="104"/>
-      <c r="O49" s="104"/>
-      <c r="P49" s="104"/>
-      <c r="Q49" s="104"/>
-      <c r="R49" s="104"/>
-      <c r="S49" s="104"/>
-      <c r="T49" s="104"/>
-      <c r="U49" s="104"/>
-      <c r="V49" s="104"/>
-      <c r="W49" s="138"/>
-      <c r="X49" s="139"/>
+      <c r="I49" s="120"/>
+      <c r="J49" s="121"/>
+      <c r="K49" s="121"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="121"/>
+      <c r="P49" s="121"/>
+      <c r="Q49" s="121"/>
+      <c r="R49" s="121"/>
+      <c r="S49" s="121"/>
+      <c r="T49" s="121"/>
+      <c r="U49" s="121"/>
+      <c r="V49" s="121"/>
+      <c r="W49" s="136"/>
+      <c r="X49" s="137"/>
       <c r="Y49" s="135"/>
       <c r="Z49" s="135"/>
       <c r="AA49" s="135"/>
@@ -10668,18 +10597,18 @@
       <c r="H50" s="108"/>
       <c r="I50" s="122"/>
       <c r="J50" s="104"/>
-      <c r="K50" s="123"/>
-      <c r="L50" s="123"/>
-      <c r="M50" s="123"/>
-      <c r="N50" s="123"/>
-      <c r="O50" s="123"/>
-      <c r="P50" s="123"/>
-      <c r="Q50" s="123"/>
-      <c r="R50" s="123"/>
-      <c r="S50" s="123"/>
-      <c r="T50" s="123"/>
-      <c r="U50" s="123"/>
-      <c r="V50" s="123"/>
+      <c r="K50" s="104"/>
+      <c r="L50" s="104"/>
+      <c r="M50" s="104"/>
+      <c r="N50" s="104"/>
+      <c r="O50" s="104"/>
+      <c r="P50" s="104"/>
+      <c r="Q50" s="104"/>
+      <c r="R50" s="104"/>
+      <c r="S50" s="104"/>
+      <c r="T50" s="104"/>
+      <c r="U50" s="104"/>
+      <c r="V50" s="104"/>
       <c r="W50" s="138"/>
       <c r="X50" s="139"/>
       <c r="Y50" s="135"/>
@@ -10701,9 +10630,7 @@
       <c r="I51" s="122"/>
       <c r="J51" s="104"/>
       <c r="K51" s="123"/>
-      <c r="L51" s="124" t="s">
-        <v>65</v>
-      </c>
+      <c r="L51" s="123"/>
       <c r="M51" s="123"/>
       <c r="N51" s="123"/>
       <c r="O51" s="123"/>
@@ -10735,7 +10662,9 @@
       <c r="I52" s="122"/>
       <c r="J52" s="104"/>
       <c r="K52" s="123"/>
-      <c r="L52" s="123"/>
+      <c r="L52" s="124" t="s">
+        <v>51</v>
+      </c>
       <c r="M52" s="123"/>
       <c r="N52" s="123"/>
       <c r="O52" s="123"/>
@@ -10766,18 +10695,18 @@
       <c r="H53" s="108"/>
       <c r="I53" s="122"/>
       <c r="J53" s="104"/>
-      <c r="K53" s="104"/>
-      <c r="L53" s="104"/>
-      <c r="M53" s="104"/>
-      <c r="N53" s="104"/>
-      <c r="O53" s="104"/>
-      <c r="P53" s="104"/>
-      <c r="Q53" s="104"/>
-      <c r="R53" s="104"/>
-      <c r="S53" s="104"/>
-      <c r="T53" s="104"/>
-      <c r="U53" s="104"/>
-      <c r="V53" s="104"/>
+      <c r="K53" s="123"/>
+      <c r="L53" s="123"/>
+      <c r="M53" s="123"/>
+      <c r="N53" s="123"/>
+      <c r="O53" s="123"/>
+      <c r="P53" s="123"/>
+      <c r="Q53" s="123"/>
+      <c r="R53" s="123"/>
+      <c r="S53" s="123"/>
+      <c r="T53" s="123"/>
+      <c r="U53" s="123"/>
+      <c r="V53" s="123"/>
       <c r="W53" s="138"/>
       <c r="X53" s="139"/>
       <c r="Y53" s="135"/>
@@ -10798,18 +10727,18 @@
       <c r="H54" s="108"/>
       <c r="I54" s="122"/>
       <c r="J54" s="104"/>
-      <c r="K54" s="123"/>
-      <c r="L54" s="123"/>
-      <c r="M54" s="123"/>
-      <c r="N54" s="123"/>
-      <c r="O54" s="123"/>
-      <c r="P54" s="123"/>
-      <c r="Q54" s="123"/>
-      <c r="R54" s="123"/>
-      <c r="S54" s="123"/>
-      <c r="T54" s="123"/>
-      <c r="U54" s="123"/>
-      <c r="V54" s="123"/>
+      <c r="K54" s="104"/>
+      <c r="L54" s="104"/>
+      <c r="M54" s="104"/>
+      <c r="N54" s="104"/>
+      <c r="O54" s="104"/>
+      <c r="P54" s="104"/>
+      <c r="Q54" s="104"/>
+      <c r="R54" s="104"/>
+      <c r="S54" s="104"/>
+      <c r="T54" s="104"/>
+      <c r="U54" s="104"/>
+      <c r="V54" s="104"/>
       <c r="W54" s="138"/>
       <c r="X54" s="139"/>
       <c r="Y54" s="135"/>
@@ -10831,9 +10760,7 @@
       <c r="I55" s="122"/>
       <c r="J55" s="104"/>
       <c r="K55" s="123"/>
-      <c r="L55" s="124" t="s">
-        <v>66</v>
-      </c>
+      <c r="L55" s="123"/>
       <c r="M55" s="123"/>
       <c r="N55" s="123"/>
       <c r="O55" s="123"/>
@@ -10865,7 +10792,9 @@
       <c r="I56" s="122"/>
       <c r="J56" s="104"/>
       <c r="K56" s="123"/>
-      <c r="L56" s="123"/>
+      <c r="L56" s="124" t="s">
+        <v>56</v>
+      </c>
       <c r="M56" s="123"/>
       <c r="N56" s="123"/>
       <c r="O56" s="123"/>
@@ -10896,18 +10825,18 @@
       <c r="H57" s="108"/>
       <c r="I57" s="122"/>
       <c r="J57" s="104"/>
-      <c r="K57" s="104"/>
-      <c r="L57" s="104"/>
-      <c r="M57" s="104"/>
-      <c r="N57" s="104"/>
-      <c r="O57" s="104"/>
-      <c r="P57" s="104"/>
-      <c r="Q57" s="104"/>
-      <c r="R57" s="104"/>
-      <c r="S57" s="104"/>
-      <c r="T57" s="104"/>
-      <c r="U57" s="104"/>
-      <c r="V57" s="104"/>
+      <c r="K57" s="123"/>
+      <c r="L57" s="123"/>
+      <c r="M57" s="123"/>
+      <c r="N57" s="123"/>
+      <c r="O57" s="123"/>
+      <c r="P57" s="123"/>
+      <c r="Q57" s="123"/>
+      <c r="R57" s="123"/>
+      <c r="S57" s="123"/>
+      <c r="T57" s="123"/>
+      <c r="U57" s="123"/>
+      <c r="V57" s="123"/>
       <c r="W57" s="138"/>
       <c r="X57" s="139"/>
       <c r="Y57" s="135"/>
@@ -10928,18 +10857,18 @@
       <c r="H58" s="108"/>
       <c r="I58" s="122"/>
       <c r="J58" s="104"/>
-      <c r="K58" s="125"/>
-      <c r="L58" s="125"/>
-      <c r="M58" s="125"/>
-      <c r="N58" s="125"/>
-      <c r="O58" s="125"/>
-      <c r="P58" s="125"/>
-      <c r="Q58" s="125"/>
-      <c r="R58" s="125"/>
-      <c r="S58" s="125"/>
-      <c r="T58" s="125"/>
-      <c r="U58" s="125"/>
-      <c r="V58" s="125"/>
+      <c r="K58" s="104"/>
+      <c r="L58" s="104"/>
+      <c r="M58" s="104"/>
+      <c r="N58" s="104"/>
+      <c r="O58" s="104"/>
+      <c r="P58" s="104"/>
+      <c r="Q58" s="104"/>
+      <c r="R58" s="104"/>
+      <c r="S58" s="104"/>
+      <c r="T58" s="104"/>
+      <c r="U58" s="104"/>
+      <c r="V58" s="104"/>
       <c r="W58" s="138"/>
       <c r="X58" s="139"/>
       <c r="Y58" s="135"/>
@@ -10965,9 +10894,7 @@
       <c r="M59" s="125"/>
       <c r="N59" s="125"/>
       <c r="O59" s="125"/>
-      <c r="P59" s="126" t="s">
-        <v>67</v>
-      </c>
+      <c r="P59" s="125"/>
       <c r="Q59" s="125"/>
       <c r="R59" s="125"/>
       <c r="S59" s="125"/>
@@ -10999,7 +10926,9 @@
       <c r="M60" s="125"/>
       <c r="N60" s="125"/>
       <c r="O60" s="125"/>
-      <c r="P60" s="125"/>
+      <c r="P60" s="126" t="s">
+        <v>57</v>
+      </c>
       <c r="Q60" s="125"/>
       <c r="R60" s="125"/>
       <c r="S60" s="125"/>
@@ -11025,20 +10954,20 @@
       <c r="G61" s="108"/>
       <c r="H61" s="108"/>
       <c r="I61" s="122"/>
-      <c r="J61" s="127"/>
-      <c r="K61" s="127"/>
-      <c r="L61" s="127"/>
-      <c r="M61" s="127"/>
-      <c r="N61" s="127"/>
-      <c r="O61" s="127"/>
-      <c r="P61" s="127"/>
-      <c r="Q61" s="127"/>
-      <c r="R61" s="127"/>
-      <c r="S61" s="127"/>
-      <c r="T61" s="127"/>
-      <c r="U61" s="127"/>
-      <c r="V61" s="127"/>
-      <c r="W61" s="140"/>
+      <c r="J61" s="104"/>
+      <c r="K61" s="125"/>
+      <c r="L61" s="125"/>
+      <c r="M61" s="125"/>
+      <c r="N61" s="125"/>
+      <c r="O61" s="125"/>
+      <c r="P61" s="125"/>
+      <c r="Q61" s="125"/>
+      <c r="R61" s="125"/>
+      <c r="S61" s="125"/>
+      <c r="T61" s="125"/>
+      <c r="U61" s="125"/>
+      <c r="V61" s="125"/>
+      <c r="W61" s="138"/>
       <c r="X61" s="139"/>
       <c r="Y61" s="135"/>
       <c r="Z61" s="135"/>
@@ -11056,11 +10985,22 @@
       <c r="F62" s="108"/>
       <c r="G62" s="108"/>
       <c r="H62" s="108"/>
-      <c r="I62" s="128"/>
-      <c r="M62" s="129" t="s">
-        <v>68</v>
-      </c>
-      <c r="X62" s="141"/>
+      <c r="I62" s="122"/>
+      <c r="J62" s="127"/>
+      <c r="K62" s="127"/>
+      <c r="L62" s="127"/>
+      <c r="M62" s="127"/>
+      <c r="N62" s="127"/>
+      <c r="O62" s="127"/>
+      <c r="P62" s="127"/>
+      <c r="Q62" s="127"/>
+      <c r="R62" s="127"/>
+      <c r="S62" s="127"/>
+      <c r="T62" s="127"/>
+      <c r="U62" s="127"/>
+      <c r="V62" s="127"/>
+      <c r="W62" s="140"/>
+      <c r="X62" s="139"/>
       <c r="Y62" s="135"/>
       <c r="Z62" s="135"/>
       <c r="AA62" s="135"/>
@@ -11078,6 +11018,9 @@
       <c r="G63" s="108"/>
       <c r="H63" s="108"/>
       <c r="I63" s="128"/>
+      <c r="M63" s="129" t="s">
+        <v>64</v>
+      </c>
       <c r="X63" s="141"/>
       <c r="Y63" s="135"/>
       <c r="Z63" s="135"/>
@@ -11095,22 +11038,8 @@
       <c r="F64" s="108"/>
       <c r="G64" s="108"/>
       <c r="H64" s="108"/>
-      <c r="I64" s="130"/>
-      <c r="J64" s="131"/>
-      <c r="K64" s="131"/>
-      <c r="L64" s="131"/>
-      <c r="M64" s="131"/>
-      <c r="N64" s="131"/>
-      <c r="O64" s="131"/>
-      <c r="P64" s="131"/>
-      <c r="Q64" s="131"/>
-      <c r="R64" s="131"/>
-      <c r="S64" s="131"/>
-      <c r="T64" s="131"/>
-      <c r="U64" s="131"/>
-      <c r="V64" s="131"/>
-      <c r="W64" s="131"/>
-      <c r="X64" s="142"/>
+      <c r="I64" s="128"/>
+      <c r="X64" s="141"/>
       <c r="Y64" s="135"/>
       <c r="Z64" s="135"/>
       <c r="AA64" s="135"/>
@@ -11121,36 +11050,36 @@
       <c r="AF64" s="145"/>
     </row>
     <row r="65" customHeight="1" spans="3:32">
-      <c r="C65" s="109"/>
-      <c r="D65" s="110"/>
-      <c r="E65" s="110"/>
-      <c r="F65" s="110"/>
-      <c r="G65" s="110"/>
-      <c r="H65" s="110"/>
-      <c r="I65" s="110"/>
-      <c r="J65" s="110"/>
-      <c r="K65" s="110"/>
-      <c r="L65" s="110"/>
-      <c r="M65" s="110"/>
-      <c r="N65" s="110"/>
-      <c r="O65" s="110"/>
-      <c r="P65" s="110"/>
-      <c r="Q65" s="110"/>
-      <c r="R65" s="110"/>
-      <c r="S65" s="110"/>
-      <c r="T65" s="110"/>
-      <c r="U65" s="110"/>
-      <c r="V65" s="110"/>
-      <c r="W65" s="110"/>
-      <c r="X65" s="110"/>
-      <c r="Y65" s="110"/>
-      <c r="Z65" s="110"/>
-      <c r="AA65" s="110"/>
-      <c r="AB65" s="110"/>
-      <c r="AC65" s="110"/>
-      <c r="AD65" s="110"/>
-      <c r="AE65" s="110"/>
-      <c r="AF65" s="146"/>
+      <c r="C65" s="107"/>
+      <c r="D65" s="108"/>
+      <c r="E65" s="108"/>
+      <c r="F65" s="108"/>
+      <c r="G65" s="108"/>
+      <c r="H65" s="108"/>
+      <c r="I65" s="130"/>
+      <c r="J65" s="131"/>
+      <c r="K65" s="131"/>
+      <c r="L65" s="131"/>
+      <c r="M65" s="131"/>
+      <c r="N65" s="131"/>
+      <c r="O65" s="131"/>
+      <c r="P65" s="131"/>
+      <c r="Q65" s="131"/>
+      <c r="R65" s="131"/>
+      <c r="S65" s="131"/>
+      <c r="T65" s="131"/>
+      <c r="U65" s="131"/>
+      <c r="V65" s="131"/>
+      <c r="W65" s="131"/>
+      <c r="X65" s="142"/>
+      <c r="Y65" s="135"/>
+      <c r="Z65" s="135"/>
+      <c r="AA65" s="135"/>
+      <c r="AB65" s="135"/>
+      <c r="AC65" s="135"/>
+      <c r="AD65" s="135"/>
+      <c r="AE65" s="135"/>
+      <c r="AF65" s="145"/>
     </row>
     <row r="66" customHeight="1" spans="3:32">
       <c r="C66" s="109"/>
@@ -11217,799 +11146,74 @@
       <c r="AF67" s="146"/>
     </row>
     <row r="68" customHeight="1" spans="3:32">
-      <c r="C68" s="111"/>
-      <c r="D68" s="112"/>
-      <c r="E68" s="112"/>
-      <c r="F68" s="112"/>
-      <c r="G68" s="112"/>
-      <c r="H68" s="112"/>
-      <c r="I68" s="112"/>
-      <c r="J68" s="112"/>
-      <c r="K68" s="112"/>
-      <c r="L68" s="112"/>
-      <c r="M68" s="112"/>
-      <c r="N68" s="112"/>
-      <c r="O68" s="112"/>
-      <c r="P68" s="112"/>
-      <c r="Q68" s="112"/>
-      <c r="R68" s="112"/>
-      <c r="S68" s="112"/>
-      <c r="T68" s="112"/>
-      <c r="U68" s="112"/>
-      <c r="V68" s="112"/>
-      <c r="W68" s="112"/>
-      <c r="X68" s="112"/>
-      <c r="Y68" s="112"/>
-      <c r="Z68" s="112"/>
-      <c r="AA68" s="112"/>
-      <c r="AB68" s="112"/>
-      <c r="AC68" s="112"/>
-      <c r="AD68" s="112"/>
-      <c r="AE68" s="112"/>
-      <c r="AF68" s="147"/>
+      <c r="C68" s="109"/>
+      <c r="D68" s="110"/>
+      <c r="E68" s="110"/>
+      <c r="F68" s="110"/>
+      <c r="G68" s="110"/>
+      <c r="H68" s="110"/>
+      <c r="I68" s="110"/>
+      <c r="J68" s="110"/>
+      <c r="K68" s="110"/>
+      <c r="L68" s="110"/>
+      <c r="M68" s="110"/>
+      <c r="N68" s="110"/>
+      <c r="O68" s="110"/>
+      <c r="P68" s="110"/>
+      <c r="Q68" s="110"/>
+      <c r="R68" s="110"/>
+      <c r="S68" s="110"/>
+      <c r="T68" s="110"/>
+      <c r="U68" s="110"/>
+      <c r="V68" s="110"/>
+      <c r="W68" s="110"/>
+      <c r="X68" s="110"/>
+      <c r="Y68" s="110"/>
+      <c r="Z68" s="110"/>
+      <c r="AA68" s="110"/>
+      <c r="AB68" s="110"/>
+      <c r="AC68" s="110"/>
+      <c r="AD68" s="110"/>
+      <c r="AE68" s="110"/>
+      <c r="AF68" s="146"/>
+    </row>
+    <row r="69" customHeight="1" spans="3:32">
+      <c r="C69" s="111"/>
+      <c r="D69" s="112"/>
+      <c r="E69" s="112"/>
+      <c r="F69" s="112"/>
+      <c r="G69" s="112"/>
+      <c r="H69" s="112"/>
+      <c r="I69" s="112"/>
+      <c r="J69" s="112"/>
+      <c r="K69" s="112"/>
+      <c r="L69" s="112"/>
+      <c r="M69" s="112"/>
+      <c r="N69" s="112"/>
+      <c r="O69" s="112"/>
+      <c r="P69" s="112"/>
+      <c r="Q69" s="112"/>
+      <c r="R69" s="112"/>
+      <c r="S69" s="112"/>
+      <c r="T69" s="112"/>
+      <c r="U69" s="112"/>
+      <c r="V69" s="112"/>
+      <c r="W69" s="112"/>
+      <c r="X69" s="112"/>
+      <c r="Y69" s="112"/>
+      <c r="Z69" s="112"/>
+      <c r="AA69" s="112"/>
+      <c r="AB69" s="112"/>
+      <c r="AC69" s="112"/>
+      <c r="AD69" s="112"/>
+      <c r="AE69" s="112"/>
+      <c r="AF69" s="147"/>
     </row>
     <row r="71" customHeight="1" spans="2:2">
       <c r="B71" s="104"/>
     </row>
     <row r="73" customHeight="1" spans="2:2">
       <c r="B73" s="104"/>
-    </row>
-    <row r="80" customHeight="1" spans="2:3">
-      <c r="B80" s="87" t="s">
-        <v>72</v>
-      </c>
-      <c r="C80" s="104"/>
-    </row>
-    <row r="81" customHeight="1" spans="3:32">
-      <c r="C81" s="105"/>
-      <c r="D81" s="106"/>
-      <c r="E81" s="106"/>
-      <c r="F81" s="106"/>
-      <c r="G81" s="106"/>
-      <c r="H81" s="106"/>
-      <c r="I81" s="106"/>
-      <c r="J81" s="106"/>
-      <c r="K81" s="106"/>
-      <c r="L81" s="106"/>
-      <c r="M81" s="106"/>
-      <c r="N81" s="106"/>
-      <c r="O81" s="106"/>
-      <c r="P81" s="106"/>
-      <c r="Q81" s="106"/>
-      <c r="R81" s="106"/>
-      <c r="S81" s="106"/>
-      <c r="T81" s="106"/>
-      <c r="U81" s="106"/>
-      <c r="V81" s="106"/>
-      <c r="W81" s="134"/>
-      <c r="X81" s="134"/>
-      <c r="Y81" s="134"/>
-      <c r="Z81" s="134"/>
-      <c r="AA81" s="134"/>
-      <c r="AB81" s="134"/>
-      <c r="AC81" s="134"/>
-      <c r="AD81" s="134"/>
-      <c r="AE81" s="134"/>
-      <c r="AF81" s="144"/>
-    </row>
-    <row r="82" customHeight="1" spans="3:32">
-      <c r="C82" s="107"/>
-      <c r="D82" s="108"/>
-      <c r="E82" s="108"/>
-      <c r="F82" s="108"/>
-      <c r="G82" s="108"/>
-      <c r="H82" s="108"/>
-      <c r="I82" s="108"/>
-      <c r="J82" s="108"/>
-      <c r="K82" s="108"/>
-      <c r="L82" s="108"/>
-      <c r="M82" s="108"/>
-      <c r="N82" s="108"/>
-      <c r="O82" s="108"/>
-      <c r="P82" s="108"/>
-      <c r="Q82" s="108"/>
-      <c r="R82" s="108"/>
-      <c r="S82" s="108"/>
-      <c r="T82" s="108"/>
-      <c r="U82" s="108"/>
-      <c r="V82" s="108"/>
-      <c r="W82" s="135"/>
-      <c r="X82" s="135"/>
-      <c r="Y82" s="135"/>
-      <c r="Z82" s="135"/>
-      <c r="AA82" s="135"/>
-      <c r="AB82" s="135"/>
-      <c r="AC82" s="135"/>
-      <c r="AD82" s="135"/>
-      <c r="AE82" s="135"/>
-      <c r="AF82" s="145"/>
-    </row>
-    <row r="83" customHeight="1" spans="3:32">
-      <c r="C83" s="107"/>
-      <c r="D83" s="108"/>
-      <c r="E83" s="108"/>
-      <c r="F83" s="108"/>
-      <c r="G83" s="108"/>
-      <c r="H83" s="108"/>
-      <c r="I83" s="108"/>
-      <c r="J83" s="108"/>
-      <c r="K83" s="108"/>
-      <c r="L83" s="108"/>
-      <c r="M83" s="132" t="s">
-        <v>71</v>
-      </c>
-      <c r="N83" s="108"/>
-      <c r="O83" s="108"/>
-      <c r="P83" s="108"/>
-      <c r="Q83" s="108"/>
-      <c r="R83" s="108"/>
-      <c r="S83" s="108"/>
-      <c r="T83" s="108"/>
-      <c r="U83" s="108"/>
-      <c r="V83" s="108"/>
-      <c r="W83" s="135"/>
-      <c r="X83" s="135"/>
-      <c r="Y83" s="135"/>
-      <c r="Z83" s="135"/>
-      <c r="AA83" s="135"/>
-      <c r="AB83" s="135"/>
-      <c r="AC83" s="135"/>
-      <c r="AD83" s="135"/>
-      <c r="AE83" s="135"/>
-      <c r="AF83" s="145"/>
-    </row>
-    <row r="84" customHeight="1" spans="3:32">
-      <c r="C84" s="107"/>
-      <c r="D84" s="108"/>
-      <c r="E84" s="108"/>
-      <c r="F84" s="108"/>
-      <c r="G84" s="108"/>
-      <c r="H84" s="108"/>
-      <c r="I84" s="120"/>
-      <c r="J84" s="121"/>
-      <c r="K84" s="121"/>
-      <c r="L84" s="121"/>
-      <c r="M84" s="121"/>
-      <c r="N84" s="121"/>
-      <c r="O84" s="121"/>
-      <c r="P84" s="121"/>
-      <c r="Q84" s="121"/>
-      <c r="R84" s="121"/>
-      <c r="S84" s="121"/>
-      <c r="T84" s="121"/>
-      <c r="U84" s="121"/>
-      <c r="V84" s="121"/>
-      <c r="W84" s="136"/>
-      <c r="X84" s="137"/>
-      <c r="Y84" s="135"/>
-      <c r="Z84" s="135"/>
-      <c r="AA84" s="135"/>
-      <c r="AB84" s="135"/>
-      <c r="AC84" s="135"/>
-      <c r="AD84" s="135"/>
-      <c r="AE84" s="135"/>
-      <c r="AF84" s="145"/>
-    </row>
-    <row r="85" customHeight="1" spans="3:32">
-      <c r="C85" s="107"/>
-      <c r="D85" s="108"/>
-      <c r="E85" s="108"/>
-      <c r="F85" s="108"/>
-      <c r="G85" s="108"/>
-      <c r="H85" s="108"/>
-      <c r="I85" s="122"/>
-      <c r="J85" s="104"/>
-      <c r="K85" s="104"/>
-      <c r="L85" s="104"/>
-      <c r="M85" s="104"/>
-      <c r="N85" s="104"/>
-      <c r="O85" s="104"/>
-      <c r="P85" s="104"/>
-      <c r="Q85" s="104"/>
-      <c r="R85" s="104"/>
-      <c r="S85" s="104"/>
-      <c r="T85" s="104"/>
-      <c r="U85" s="104"/>
-      <c r="V85" s="104"/>
-      <c r="W85" s="138"/>
-      <c r="X85" s="139"/>
-      <c r="Y85" s="135"/>
-      <c r="Z85" s="135"/>
-      <c r="AA85" s="135"/>
-      <c r="AB85" s="135"/>
-      <c r="AC85" s="135"/>
-      <c r="AD85" s="135"/>
-      <c r="AE85" s="135"/>
-      <c r="AF85" s="145"/>
-    </row>
-    <row r="86" customHeight="1" spans="3:32">
-      <c r="C86" s="107"/>
-      <c r="D86" s="108"/>
-      <c r="E86" s="108"/>
-      <c r="F86" s="108"/>
-      <c r="G86" s="108"/>
-      <c r="H86" s="108"/>
-      <c r="I86" s="122"/>
-      <c r="J86" s="104"/>
-      <c r="K86" s="123"/>
-      <c r="L86" s="123"/>
-      <c r="M86" s="123"/>
-      <c r="N86" s="123"/>
-      <c r="O86" s="123"/>
-      <c r="P86" s="123"/>
-      <c r="Q86" s="123"/>
-      <c r="R86" s="123"/>
-      <c r="S86" s="123"/>
-      <c r="T86" s="123"/>
-      <c r="U86" s="123"/>
-      <c r="V86" s="123"/>
-      <c r="W86" s="138"/>
-      <c r="X86" s="139"/>
-      <c r="Y86" s="135"/>
-      <c r="Z86" s="135"/>
-      <c r="AA86" s="135"/>
-      <c r="AB86" s="135"/>
-      <c r="AC86" s="135"/>
-      <c r="AD86" s="135"/>
-      <c r="AE86" s="135"/>
-      <c r="AF86" s="145"/>
-    </row>
-    <row r="87" customHeight="1" spans="3:32">
-      <c r="C87" s="107"/>
-      <c r="D87" s="108"/>
-      <c r="E87" s="108"/>
-      <c r="F87" s="108"/>
-      <c r="G87" s="108"/>
-      <c r="H87" s="108"/>
-      <c r="I87" s="122"/>
-      <c r="J87" s="104"/>
-      <c r="K87" s="123"/>
-      <c r="L87" s="124" t="s">
-        <v>65</v>
-      </c>
-      <c r="M87" s="123"/>
-      <c r="N87" s="123"/>
-      <c r="O87" s="123"/>
-      <c r="P87" s="123"/>
-      <c r="Q87" s="123"/>
-      <c r="R87" s="123"/>
-      <c r="S87" s="123"/>
-      <c r="T87" s="123"/>
-      <c r="U87" s="123"/>
-      <c r="V87" s="123"/>
-      <c r="W87" s="138"/>
-      <c r="X87" s="139"/>
-      <c r="Y87" s="135"/>
-      <c r="Z87" s="135"/>
-      <c r="AA87" s="135"/>
-      <c r="AB87" s="135"/>
-      <c r="AC87" s="135"/>
-      <c r="AD87" s="135"/>
-      <c r="AE87" s="135"/>
-      <c r="AF87" s="145"/>
-    </row>
-    <row r="88" customHeight="1" spans="3:32">
-      <c r="C88" s="107"/>
-      <c r="D88" s="108"/>
-      <c r="E88" s="108"/>
-      <c r="F88" s="108"/>
-      <c r="G88" s="108"/>
-      <c r="H88" s="108"/>
-      <c r="I88" s="122"/>
-      <c r="J88" s="104"/>
-      <c r="K88" s="123"/>
-      <c r="L88" s="123"/>
-      <c r="M88" s="123"/>
-      <c r="N88" s="123"/>
-      <c r="O88" s="123"/>
-      <c r="P88" s="123"/>
-      <c r="Q88" s="123"/>
-      <c r="R88" s="123"/>
-      <c r="S88" s="123"/>
-      <c r="T88" s="123"/>
-      <c r="U88" s="123"/>
-      <c r="V88" s="123"/>
-      <c r="W88" s="138"/>
-      <c r="X88" s="139"/>
-      <c r="Y88" s="135"/>
-      <c r="Z88" s="135"/>
-      <c r="AA88" s="135"/>
-      <c r="AB88" s="135"/>
-      <c r="AC88" s="135"/>
-      <c r="AD88" s="135"/>
-      <c r="AE88" s="135"/>
-      <c r="AF88" s="145"/>
-    </row>
-    <row r="89" customHeight="1" spans="3:32">
-      <c r="C89" s="107"/>
-      <c r="D89" s="108"/>
-      <c r="E89" s="108"/>
-      <c r="F89" s="108"/>
-      <c r="G89" s="108"/>
-      <c r="H89" s="108"/>
-      <c r="I89" s="122"/>
-      <c r="J89" s="104"/>
-      <c r="K89" s="104"/>
-      <c r="L89" s="104"/>
-      <c r="M89" s="104"/>
-      <c r="N89" s="104"/>
-      <c r="O89" s="104"/>
-      <c r="P89" s="104"/>
-      <c r="Q89" s="104"/>
-      <c r="R89" s="104"/>
-      <c r="S89" s="104"/>
-      <c r="T89" s="104"/>
-      <c r="U89" s="104"/>
-      <c r="V89" s="104"/>
-      <c r="W89" s="138"/>
-      <c r="X89" s="139"/>
-      <c r="Y89" s="135"/>
-      <c r="Z89" s="135"/>
-      <c r="AA89" s="135"/>
-      <c r="AB89" s="135"/>
-      <c r="AC89" s="135"/>
-      <c r="AD89" s="135"/>
-      <c r="AE89" s="135"/>
-      <c r="AF89" s="145"/>
-    </row>
-    <row r="90" customHeight="1" spans="3:32">
-      <c r="C90" s="107"/>
-      <c r="D90" s="108"/>
-      <c r="E90" s="108"/>
-      <c r="F90" s="108"/>
-      <c r="G90" s="108"/>
-      <c r="H90" s="108"/>
-      <c r="I90" s="122"/>
-      <c r="J90" s="104"/>
-      <c r="K90" s="123"/>
-      <c r="L90" s="123"/>
-      <c r="M90" s="123"/>
-      <c r="N90" s="123"/>
-      <c r="O90" s="123"/>
-      <c r="P90" s="123"/>
-      <c r="Q90" s="123"/>
-      <c r="R90" s="123"/>
-      <c r="S90" s="123"/>
-      <c r="T90" s="123"/>
-      <c r="U90" s="123"/>
-      <c r="V90" s="123"/>
-      <c r="W90" s="138"/>
-      <c r="X90" s="139"/>
-      <c r="Y90" s="135"/>
-      <c r="Z90" s="135"/>
-      <c r="AA90" s="135"/>
-      <c r="AB90" s="135"/>
-      <c r="AC90" s="135"/>
-      <c r="AD90" s="135"/>
-      <c r="AE90" s="135"/>
-      <c r="AF90" s="145"/>
-    </row>
-    <row r="91" customHeight="1" spans="3:32">
-      <c r="C91" s="107"/>
-      <c r="D91" s="108"/>
-      <c r="E91" s="108"/>
-      <c r="F91" s="108"/>
-      <c r="G91" s="108"/>
-      <c r="H91" s="108"/>
-      <c r="I91" s="122"/>
-      <c r="J91" s="104"/>
-      <c r="K91" s="123"/>
-      <c r="L91" s="124" t="s">
-        <v>66</v>
-      </c>
-      <c r="M91" s="123"/>
-      <c r="N91" s="123"/>
-      <c r="O91" s="123"/>
-      <c r="P91" s="123"/>
-      <c r="Q91" s="123"/>
-      <c r="R91" s="123"/>
-      <c r="S91" s="123"/>
-      <c r="T91" s="123"/>
-      <c r="U91" s="123"/>
-      <c r="V91" s="123"/>
-      <c r="W91" s="138"/>
-      <c r="X91" s="139"/>
-      <c r="Y91" s="135"/>
-      <c r="Z91" s="135"/>
-      <c r="AA91" s="135"/>
-      <c r="AB91" s="135"/>
-      <c r="AC91" s="135"/>
-      <c r="AD91" s="135"/>
-      <c r="AE91" s="135"/>
-      <c r="AF91" s="145"/>
-    </row>
-    <row r="92" customHeight="1" spans="3:32">
-      <c r="C92" s="107"/>
-      <c r="D92" s="108"/>
-      <c r="E92" s="108"/>
-      <c r="F92" s="108"/>
-      <c r="G92" s="108"/>
-      <c r="H92" s="108"/>
-      <c r="I92" s="122"/>
-      <c r="J92" s="104"/>
-      <c r="K92" s="123"/>
-      <c r="L92" s="123"/>
-      <c r="M92" s="123"/>
-      <c r="N92" s="123"/>
-      <c r="O92" s="123"/>
-      <c r="P92" s="123"/>
-      <c r="Q92" s="123"/>
-      <c r="R92" s="123"/>
-      <c r="S92" s="123"/>
-      <c r="T92" s="123"/>
-      <c r="U92" s="123"/>
-      <c r="V92" s="123"/>
-      <c r="W92" s="138"/>
-      <c r="X92" s="139"/>
-      <c r="Y92" s="135"/>
-      <c r="Z92" s="135"/>
-      <c r="AA92" s="135"/>
-      <c r="AB92" s="135"/>
-      <c r="AC92" s="135"/>
-      <c r="AD92" s="135"/>
-      <c r="AE92" s="135"/>
-      <c r="AF92" s="145"/>
-    </row>
-    <row r="93" customHeight="1" spans="3:32">
-      <c r="C93" s="107"/>
-      <c r="D93" s="108"/>
-      <c r="E93" s="108"/>
-      <c r="F93" s="108"/>
-      <c r="G93" s="108"/>
-      <c r="H93" s="108"/>
-      <c r="I93" s="122"/>
-      <c r="J93" s="104"/>
-      <c r="K93" s="104"/>
-      <c r="L93" s="104"/>
-      <c r="M93" s="104"/>
-      <c r="N93" s="104"/>
-      <c r="O93" s="104"/>
-      <c r="P93" s="104"/>
-      <c r="Q93" s="104"/>
-      <c r="R93" s="104"/>
-      <c r="S93" s="104"/>
-      <c r="T93" s="104"/>
-      <c r="U93" s="104"/>
-      <c r="V93" s="104"/>
-      <c r="W93" s="138"/>
-      <c r="X93" s="139"/>
-      <c r="Y93" s="135"/>
-      <c r="Z93" s="135"/>
-      <c r="AA93" s="135"/>
-      <c r="AB93" s="135"/>
-      <c r="AC93" s="135"/>
-      <c r="AD93" s="135"/>
-      <c r="AE93" s="135"/>
-      <c r="AF93" s="145"/>
-    </row>
-    <row r="94" customHeight="1" spans="3:32">
-      <c r="C94" s="107"/>
-      <c r="D94" s="108"/>
-      <c r="E94" s="108"/>
-      <c r="F94" s="108"/>
-      <c r="G94" s="108"/>
-      <c r="H94" s="108"/>
-      <c r="I94" s="122"/>
-      <c r="J94" s="104"/>
-      <c r="K94" s="125"/>
-      <c r="L94" s="125"/>
-      <c r="M94" s="125"/>
-      <c r="N94" s="125"/>
-      <c r="O94" s="125"/>
-      <c r="P94" s="125"/>
-      <c r="Q94" s="125"/>
-      <c r="R94" s="125"/>
-      <c r="S94" s="125"/>
-      <c r="T94" s="125"/>
-      <c r="U94" s="125"/>
-      <c r="V94" s="125"/>
-      <c r="W94" s="138"/>
-      <c r="X94" s="139"/>
-      <c r="Y94" s="135"/>
-      <c r="Z94" s="135"/>
-      <c r="AA94" s="135"/>
-      <c r="AB94" s="135"/>
-      <c r="AC94" s="135"/>
-      <c r="AD94" s="135"/>
-      <c r="AE94" s="135"/>
-      <c r="AF94" s="145"/>
-    </row>
-    <row r="95" customHeight="1" spans="3:32">
-      <c r="C95" s="107"/>
-      <c r="D95" s="108"/>
-      <c r="E95" s="108"/>
-      <c r="F95" s="108"/>
-      <c r="G95" s="108"/>
-      <c r="H95" s="108"/>
-      <c r="I95" s="122"/>
-      <c r="J95" s="104"/>
-      <c r="K95" s="125"/>
-      <c r="L95" s="125"/>
-      <c r="M95" s="125"/>
-      <c r="N95" s="125"/>
-      <c r="O95" s="125"/>
-      <c r="P95" s="126" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q95" s="125"/>
-      <c r="R95" s="125"/>
-      <c r="S95" s="125"/>
-      <c r="T95" s="125"/>
-      <c r="U95" s="125"/>
-      <c r="V95" s="125"/>
-      <c r="W95" s="138"/>
-      <c r="X95" s="139"/>
-      <c r="Y95" s="135"/>
-      <c r="Z95" s="135"/>
-      <c r="AA95" s="135"/>
-      <c r="AB95" s="135"/>
-      <c r="AC95" s="135"/>
-      <c r="AD95" s="135"/>
-      <c r="AE95" s="135"/>
-      <c r="AF95" s="145"/>
-    </row>
-    <row r="96" customHeight="1" spans="3:32">
-      <c r="C96" s="107"/>
-      <c r="D96" s="108"/>
-      <c r="E96" s="108"/>
-      <c r="F96" s="108"/>
-      <c r="G96" s="108"/>
-      <c r="H96" s="108"/>
-      <c r="I96" s="122"/>
-      <c r="J96" s="104"/>
-      <c r="K96" s="125"/>
-      <c r="L96" s="125"/>
-      <c r="M96" s="125"/>
-      <c r="N96" s="125"/>
-      <c r="O96" s="125"/>
-      <c r="P96" s="125"/>
-      <c r="Q96" s="125"/>
-      <c r="R96" s="125"/>
-      <c r="S96" s="125"/>
-      <c r="T96" s="125"/>
-      <c r="U96" s="125"/>
-      <c r="V96" s="125"/>
-      <c r="W96" s="138"/>
-      <c r="X96" s="139"/>
-      <c r="Y96" s="135"/>
-      <c r="Z96" s="135"/>
-      <c r="AA96" s="135"/>
-      <c r="AB96" s="135"/>
-      <c r="AC96" s="135"/>
-      <c r="AD96" s="135"/>
-      <c r="AE96" s="135"/>
-      <c r="AF96" s="145"/>
-    </row>
-    <row r="97" customHeight="1" spans="3:32">
-      <c r="C97" s="107"/>
-      <c r="D97" s="108"/>
-      <c r="E97" s="108"/>
-      <c r="F97" s="108"/>
-      <c r="G97" s="108"/>
-      <c r="H97" s="108"/>
-      <c r="I97" s="122"/>
-      <c r="J97" s="127"/>
-      <c r="K97" s="127"/>
-      <c r="L97" s="127"/>
-      <c r="M97" s="127"/>
-      <c r="N97" s="127"/>
-      <c r="O97" s="127"/>
-      <c r="P97" s="127"/>
-      <c r="Q97" s="127"/>
-      <c r="R97" s="127"/>
-      <c r="S97" s="127"/>
-      <c r="T97" s="127"/>
-      <c r="U97" s="127"/>
-      <c r="V97" s="127"/>
-      <c r="W97" s="140"/>
-      <c r="X97" s="139"/>
-      <c r="Y97" s="135"/>
-      <c r="Z97" s="135"/>
-      <c r="AA97" s="135"/>
-      <c r="AB97" s="135"/>
-      <c r="AC97" s="135"/>
-      <c r="AD97" s="135"/>
-      <c r="AE97" s="135"/>
-      <c r="AF97" s="145"/>
-    </row>
-    <row r="98" customHeight="1" spans="3:32">
-      <c r="C98" s="107"/>
-      <c r="D98" s="108"/>
-      <c r="E98" s="108"/>
-      <c r="F98" s="108"/>
-      <c r="G98" s="108"/>
-      <c r="H98" s="108"/>
-      <c r="I98" s="128"/>
-      <c r="M98" s="129" t="s">
-        <v>68</v>
-      </c>
-      <c r="X98" s="141"/>
-      <c r="Y98" s="135"/>
-      <c r="Z98" s="135"/>
-      <c r="AA98" s="135"/>
-      <c r="AB98" s="135"/>
-      <c r="AC98" s="135"/>
-      <c r="AD98" s="135"/>
-      <c r="AE98" s="135"/>
-      <c r="AF98" s="145"/>
-    </row>
-    <row r="99" customHeight="1" spans="3:32">
-      <c r="C99" s="107"/>
-      <c r="D99" s="108"/>
-      <c r="E99" s="108"/>
-      <c r="F99" s="108"/>
-      <c r="G99" s="108"/>
-      <c r="H99" s="108"/>
-      <c r="I99" s="128"/>
-      <c r="X99" s="141"/>
-      <c r="Y99" s="135"/>
-      <c r="Z99" s="135"/>
-      <c r="AA99" s="135"/>
-      <c r="AB99" s="135"/>
-      <c r="AC99" s="135"/>
-      <c r="AD99" s="135"/>
-      <c r="AE99" s="135"/>
-      <c r="AF99" s="145"/>
-    </row>
-    <row r="100" customHeight="1" spans="3:32">
-      <c r="C100" s="107"/>
-      <c r="D100" s="108"/>
-      <c r="E100" s="108"/>
-      <c r="F100" s="108"/>
-      <c r="G100" s="108"/>
-      <c r="H100" s="108"/>
-      <c r="I100" s="130"/>
-      <c r="J100" s="131"/>
-      <c r="K100" s="131"/>
-      <c r="L100" s="131"/>
-      <c r="M100" s="131"/>
-      <c r="N100" s="131"/>
-      <c r="O100" s="131"/>
-      <c r="P100" s="131"/>
-      <c r="Q100" s="131"/>
-      <c r="R100" s="131"/>
-      <c r="S100" s="131"/>
-      <c r="T100" s="131"/>
-      <c r="U100" s="131"/>
-      <c r="V100" s="131"/>
-      <c r="W100" s="131"/>
-      <c r="X100" s="142"/>
-      <c r="Y100" s="135"/>
-      <c r="Z100" s="135"/>
-      <c r="AA100" s="135"/>
-      <c r="AB100" s="135"/>
-      <c r="AC100" s="135"/>
-      <c r="AD100" s="135"/>
-      <c r="AE100" s="135"/>
-      <c r="AF100" s="145"/>
-    </row>
-    <row r="101" customHeight="1" spans="3:32">
-      <c r="C101" s="109"/>
-      <c r="D101" s="110"/>
-      <c r="E101" s="110"/>
-      <c r="F101" s="110"/>
-      <c r="G101" s="110"/>
-      <c r="H101" s="110"/>
-      <c r="I101" s="110"/>
-      <c r="J101" s="110"/>
-      <c r="K101" s="110"/>
-      <c r="L101" s="110"/>
-      <c r="M101" s="110"/>
-      <c r="N101" s="110"/>
-      <c r="O101" s="110"/>
-      <c r="P101" s="110"/>
-      <c r="Q101" s="110"/>
-      <c r="R101" s="110"/>
-      <c r="S101" s="110"/>
-      <c r="T101" s="110"/>
-      <c r="U101" s="110"/>
-      <c r="V101" s="110"/>
-      <c r="W101" s="110"/>
-      <c r="X101" s="110"/>
-      <c r="Y101" s="110"/>
-      <c r="Z101" s="110"/>
-      <c r="AA101" s="110"/>
-      <c r="AB101" s="110"/>
-      <c r="AC101" s="110"/>
-      <c r="AD101" s="110"/>
-      <c r="AE101" s="110"/>
-      <c r="AF101" s="146"/>
-    </row>
-    <row r="102" customHeight="1" spans="3:32">
-      <c r="C102" s="109"/>
-      <c r="D102" s="110"/>
-      <c r="E102" s="110"/>
-      <c r="F102" s="110"/>
-      <c r="G102" s="110"/>
-      <c r="H102" s="110"/>
-      <c r="I102" s="110"/>
-      <c r="J102" s="110"/>
-      <c r="K102" s="110"/>
-      <c r="L102" s="110"/>
-      <c r="M102" s="110"/>
-      <c r="N102" s="110"/>
-      <c r="O102" s="110"/>
-      <c r="P102" s="110"/>
-      <c r="Q102" s="110"/>
-      <c r="R102" s="110"/>
-      <c r="S102" s="110"/>
-      <c r="T102" s="110"/>
-      <c r="U102" s="110"/>
-      <c r="V102" s="110"/>
-      <c r="W102" s="110"/>
-      <c r="X102" s="110"/>
-      <c r="Y102" s="110"/>
-      <c r="Z102" s="110"/>
-      <c r="AA102" s="110"/>
-      <c r="AB102" s="110"/>
-      <c r="AC102" s="110"/>
-      <c r="AD102" s="110"/>
-      <c r="AE102" s="110"/>
-      <c r="AF102" s="146"/>
-    </row>
-    <row r="103" customHeight="1" spans="3:32">
-      <c r="C103" s="109"/>
-      <c r="D103" s="110"/>
-      <c r="E103" s="110"/>
-      <c r="F103" s="110"/>
-      <c r="G103" s="110"/>
-      <c r="H103" s="110"/>
-      <c r="I103" s="110"/>
-      <c r="J103" s="110"/>
-      <c r="K103" s="110"/>
-      <c r="L103" s="110"/>
-      <c r="M103" s="110"/>
-      <c r="N103" s="110"/>
-      <c r="O103" s="110"/>
-      <c r="P103" s="110"/>
-      <c r="Q103" s="110"/>
-      <c r="R103" s="110"/>
-      <c r="S103" s="110"/>
-      <c r="T103" s="110"/>
-      <c r="U103" s="110"/>
-      <c r="V103" s="110"/>
-      <c r="W103" s="110"/>
-      <c r="X103" s="110"/>
-      <c r="Y103" s="110"/>
-      <c r="Z103" s="110"/>
-      <c r="AA103" s="110"/>
-      <c r="AB103" s="110"/>
-      <c r="AC103" s="110"/>
-      <c r="AD103" s="110"/>
-      <c r="AE103" s="110"/>
-      <c r="AF103" s="146"/>
-    </row>
-    <row r="104" customHeight="1" spans="3:32">
-      <c r="C104" s="111"/>
-      <c r="D104" s="112"/>
-      <c r="E104" s="112"/>
-      <c r="F104" s="112"/>
-      <c r="G104" s="112"/>
-      <c r="H104" s="112"/>
-      <c r="I104" s="112"/>
-      <c r="J104" s="112"/>
-      <c r="K104" s="112"/>
-      <c r="L104" s="112"/>
-      <c r="M104" s="112"/>
-      <c r="N104" s="112"/>
-      <c r="O104" s="112"/>
-      <c r="P104" s="112"/>
-      <c r="Q104" s="112"/>
-      <c r="R104" s="112"/>
-      <c r="S104" s="112"/>
-      <c r="T104" s="112"/>
-      <c r="U104" s="112"/>
-      <c r="V104" s="112"/>
-      <c r="W104" s="112"/>
-      <c r="X104" s="112"/>
-      <c r="Y104" s="112"/>
-      <c r="Z104" s="112"/>
-      <c r="AA104" s="112"/>
-      <c r="AB104" s="112"/>
-      <c r="AC104" s="112"/>
-      <c r="AD104" s="112"/>
-      <c r="AE104" s="112"/>
-      <c r="AF104" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -12059,7 +11263,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:37">
       <c r="A1" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -12254,7 +11458,7 @@
       <c r="B5" s="49"/>
       <c r="C5" s="50"/>
       <c r="D5" s="51" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E5" s="52"/>
       <c r="F5" s="53"/>
@@ -12264,7 +11468,7 @@
       <c r="H5" s="49"/>
       <c r="I5" s="50"/>
       <c r="J5" s="51" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K5" s="52"/>
       <c r="L5" s="52"/>
@@ -12296,7 +11500,7 @@
     </row>
     <row r="6" customHeight="1" spans="1:37">
       <c r="A6" s="48" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B6" s="49"/>
       <c r="C6" s="49"/>
@@ -12305,7 +11509,7 @@
       <c r="F6" s="49"/>
       <c r="G6" s="49"/>
       <c r="H6" s="48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I6" s="49"/>
       <c r="J6" s="49"/>
@@ -12331,7 +11535,7 @@
       <c r="AD6" s="49"/>
       <c r="AE6" s="49"/>
       <c r="AF6" s="48" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AG6" s="49"/>
       <c r="AH6" s="49"/>
@@ -12380,7 +11584,7 @@
     </row>
     <row r="8" customHeight="1" spans="1:37">
       <c r="A8" s="56" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B8" s="57"/>
       <c r="C8" s="57"/>
@@ -12390,7 +11594,7 @@
       <c r="G8" s="57"/>
       <c r="H8" s="10"/>
       <c r="I8" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J8" s="75"/>
       <c r="K8" s="75"/>
@@ -12432,7 +11636,7 @@
       <c r="H9" s="10"/>
       <c r="I9" s="12"/>
       <c r="J9" s="76" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K9" s="77"/>
       <c r="L9" s="77"/>
@@ -12474,7 +11678,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="76"/>
       <c r="K10" s="76" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L10" s="77"/>
       <c r="M10" s="77"/>
@@ -12515,7 +11719,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="76"/>
       <c r="K11" s="76" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L11" s="77"/>
       <c r="M11" s="77"/>
@@ -12594,7 +11798,7 @@
       <c r="H13" s="10"/>
       <c r="I13" s="12"/>
       <c r="J13" s="76" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K13" s="76"/>
       <c r="L13" s="76"/>
@@ -12636,7 +11840,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="76"/>
       <c r="K14" s="76" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L14" s="76"/>
       <c r="M14" s="76"/>
@@ -12677,7 +11881,7 @@
       <c r="I15" s="12"/>
       <c r="J15" s="76"/>
       <c r="K15" s="76" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L15" s="76"/>
       <c r="M15" s="76"/>
@@ -12756,7 +11960,7 @@
       <c r="H17" s="10"/>
       <c r="I17" s="75"/>
       <c r="J17" s="12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K17" s="75"/>
       <c r="L17" s="75"/>
@@ -12780,7 +11984,7 @@
       <c r="AD17" s="12"/>
       <c r="AE17" s="44"/>
       <c r="AF17" s="90" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AG17" s="90"/>
       <c r="AH17" s="90"/>
@@ -12829,7 +12033,7 @@
     </row>
     <row r="19" customHeight="1" spans="1:37">
       <c r="A19" s="56" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B19" s="57"/>
       <c r="C19" s="57"/>
@@ -12839,7 +12043,7 @@
       <c r="G19" s="57"/>
       <c r="H19" s="10"/>
       <c r="I19" s="12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J19" s="75"/>
       <c r="K19" s="78"/>
@@ -12873,7 +12077,7 @@
     <row r="20" customHeight="1" spans="1:37">
       <c r="A20" s="56"/>
       <c r="B20" s="65" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C20" s="57"/>
       <c r="D20" s="57"/>
@@ -12883,7 +12087,7 @@
       <c r="H20" s="10"/>
       <c r="I20" s="12"/>
       <c r="J20" s="76" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K20" s="77"/>
       <c r="L20" s="77"/>
@@ -12925,7 +12129,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="76"/>
       <c r="K21" s="76" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L21" s="77"/>
       <c r="M21" s="77"/>
@@ -12966,7 +12170,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="76"/>
       <c r="K22" s="76" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L22" s="77"/>
       <c r="M22" s="77"/>
@@ -13045,7 +12249,7 @@
       <c r="H24" s="10"/>
       <c r="I24" s="75"/>
       <c r="J24" s="12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K24" s="12"/>
       <c r="L24" s="12"/>
@@ -13087,7 +12291,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12"/>
@@ -13128,14 +12332,14 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="79" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L26" s="80"/>
       <c r="M26" s="80"/>
       <c r="N26" s="80"/>
       <c r="O26" s="81"/>
       <c r="P26" s="79" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="Q26" s="80"/>
       <c r="R26" s="80"/>
@@ -13148,7 +12352,7 @@
       <c r="Y26" s="80"/>
       <c r="Z26" s="81"/>
       <c r="AA26" s="16" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AB26" s="17"/>
       <c r="AC26" s="17"/>
@@ -13178,7 +12382,7 @@
       <c r="N27" s="83"/>
       <c r="O27" s="84"/>
       <c r="P27" s="82" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q27" s="83"/>
       <c r="R27" s="83"/>
@@ -13191,7 +12395,7 @@
       <c r="Y27" s="83"/>
       <c r="Z27" s="84"/>
       <c r="AA27" s="23" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="AB27" s="24"/>
       <c r="AC27" s="24"/>
@@ -13216,14 +12420,14 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="82" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L28" s="83"/>
       <c r="M28" s="83"/>
       <c r="N28" s="83"/>
       <c r="O28" s="84"/>
       <c r="P28" s="82" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q28" s="83"/>
       <c r="R28" s="83"/>
@@ -13236,7 +12440,7 @@
       <c r="Y28" s="83"/>
       <c r="Z28" s="84"/>
       <c r="AA28" s="23" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AB28" s="24"/>
       <c r="AC28" s="24"/>
@@ -13261,14 +12465,14 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="82" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L29" s="83"/>
       <c r="M29" s="83"/>
       <c r="N29" s="83"/>
       <c r="O29" s="84"/>
       <c r="P29" s="82" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q29" s="83"/>
       <c r="R29" s="83"/>
@@ -13304,14 +12508,14 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="82" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L30" s="83"/>
       <c r="M30" s="83"/>
       <c r="N30" s="83"/>
       <c r="O30" s="84"/>
       <c r="P30" s="82" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q30" s="83"/>
       <c r="R30" s="83"/>
@@ -13347,14 +12551,14 @@
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="82" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="L31" s="83"/>
       <c r="M31" s="83"/>
       <c r="N31" s="83"/>
       <c r="O31" s="84"/>
       <c r="P31" s="82" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q31" s="83"/>
       <c r="R31" s="83"/>
@@ -13390,14 +12594,14 @@
       <c r="I32" s="12"/>
       <c r="J32" s="12"/>
       <c r="K32" s="82" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="L32" s="83"/>
       <c r="M32" s="83"/>
       <c r="N32" s="83"/>
       <c r="O32" s="84"/>
       <c r="P32" s="82" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q32" s="83"/>
       <c r="R32" s="83"/>
@@ -13432,15 +12636,15 @@
       <c r="H33" s="10"/>
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
-      <c r="K33" s="203" t="s">
-        <v>103</v>
+      <c r="K33" s="205" t="s">
+        <v>99</v>
       </c>
       <c r="L33" s="83"/>
       <c r="M33" s="83"/>
       <c r="N33" s="83"/>
       <c r="O33" s="84"/>
       <c r="P33" s="82" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q33" s="83"/>
       <c r="R33" s="83"/>
@@ -13475,15 +12679,15 @@
       <c r="H34" s="10"/>
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
-      <c r="K34" s="203" t="s">
-        <v>104</v>
+      <c r="K34" s="205" t="s">
+        <v>100</v>
       </c>
       <c r="L34" s="83"/>
       <c r="M34" s="83"/>
       <c r="N34" s="83"/>
       <c r="O34" s="84"/>
       <c r="P34" s="82" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q34" s="83"/>
       <c r="R34" s="83"/>
@@ -13518,15 +12722,15 @@
       <c r="H35" s="10"/>
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
-      <c r="K35" s="203" t="s">
-        <v>105</v>
+      <c r="K35" s="205" t="s">
+        <v>101</v>
       </c>
       <c r="L35" s="83"/>
       <c r="M35" s="83"/>
       <c r="N35" s="83"/>
       <c r="O35" s="84"/>
       <c r="P35" s="82" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q35" s="83"/>
       <c r="R35" s="83"/>
@@ -13561,15 +12765,15 @@
       <c r="H36" s="10"/>
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
-      <c r="K36" s="203" t="s">
-        <v>106</v>
+      <c r="K36" s="205" t="s">
+        <v>102</v>
       </c>
       <c r="L36" s="83"/>
       <c r="M36" s="83"/>
       <c r="N36" s="83"/>
       <c r="O36" s="84"/>
       <c r="P36" s="82" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q36" s="83"/>
       <c r="R36" s="83"/>
@@ -13604,15 +12808,15 @@
       <c r="H37" s="10"/>
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
-      <c r="K37" s="203" t="s">
-        <v>107</v>
+      <c r="K37" s="205" t="s">
+        <v>103</v>
       </c>
       <c r="L37" s="83"/>
       <c r="M37" s="83"/>
       <c r="N37" s="83"/>
       <c r="O37" s="84"/>
       <c r="P37" s="82" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q37" s="83"/>
       <c r="R37" s="83"/>
@@ -13647,15 +12851,15 @@
       <c r="H38" s="10"/>
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
-      <c r="K38" s="203" t="s">
-        <v>108</v>
+      <c r="K38" s="205" t="s">
+        <v>104</v>
       </c>
       <c r="L38" s="83"/>
       <c r="M38" s="83"/>
       <c r="N38" s="83"/>
       <c r="O38" s="84"/>
       <c r="P38" s="82" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q38" s="83"/>
       <c r="R38" s="83"/>
@@ -13720,7 +12924,7 @@
     </row>
     <row r="40" customHeight="1" spans="1:37">
       <c r="A40" s="56" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B40" s="57"/>
       <c r="C40" s="57"/>
@@ -13731,8 +12935,8 @@
       <c r="H40" s="10"/>
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
-      <c r="K40" s="204" t="s">
-        <v>110</v>
+      <c r="K40" s="206" t="s">
+        <v>106</v>
       </c>
       <c r="L40" s="87"/>
       <c r="M40" s="88"/>
@@ -13763,7 +12967,7 @@
     </row>
     <row r="41" customHeight="1" spans="1:37">
       <c r="A41" s="56" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B41" s="57"/>
       <c r="C41" s="57"/>
@@ -13776,7 +12980,7 @@
       <c r="J41" s="12"/>
       <c r="K41" s="86"/>
       <c r="L41" s="87" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="M41" s="88"/>
       <c r="N41" s="88"/>
@@ -13807,7 +13011,7 @@
     <row r="42" customHeight="1" spans="1:37">
       <c r="A42" s="58"/>
       <c r="B42" s="59" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C42" s="60"/>
       <c r="D42" s="60"/>
@@ -13819,7 +13023,7 @@
       <c r="J42" s="12"/>
       <c r="K42" s="86"/>
       <c r="L42" s="87" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="M42" s="88"/>
       <c r="N42" s="88"/>
@@ -13850,7 +13054,7 @@
     <row r="43" customHeight="1" spans="1:37">
       <c r="A43" s="65"/>
       <c r="B43" s="65" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C43" s="72"/>
       <c r="D43" s="72"/>
@@ -13863,7 +13067,7 @@
       <c r="K43" s="86"/>
       <c r="L43" s="87"/>
       <c r="M43" s="76" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="N43" s="88"/>
       <c r="O43" s="88"/>
@@ -13904,7 +13108,7 @@
       <c r="K44" s="86"/>
       <c r="L44" s="87"/>
       <c r="M44" s="76" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="N44" s="88"/>
       <c r="O44" s="88"/>
@@ -13981,8 +13185,8 @@
       <c r="H46" s="10"/>
       <c r="I46" s="12"/>
       <c r="J46" s="12"/>
-      <c r="K46" s="204" t="s">
-        <v>116</v>
+      <c r="K46" s="206" t="s">
+        <v>112</v>
       </c>
       <c r="L46" s="85"/>
       <c r="M46" s="85"/>
@@ -14005,7 +13209,7 @@
       <c r="AD46" s="64"/>
       <c r="AE46" s="44"/>
       <c r="AF46" s="90" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AG46" s="90"/>
       <c r="AH46" s="90"/>
@@ -14063,7 +13267,7 @@
       <c r="H48" s="10"/>
       <c r="I48" s="12"/>
       <c r="J48" s="12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K48" s="12"/>
       <c r="L48" s="12"/>
@@ -14105,7 +13309,7 @@
       <c r="I49" s="12"/>
       <c r="J49" s="12"/>
       <c r="K49" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L49" s="12"/>
       <c r="M49" s="12"/>
@@ -14146,7 +13350,7 @@
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
       <c r="K50" s="12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L50" s="12"/>
       <c r="M50" s="12"/>
@@ -14226,7 +13430,7 @@
       <c r="I52" s="12"/>
       <c r="J52" s="12"/>
       <c r="K52" s="12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L52" s="12"/>
       <c r="M52" s="12"/>
@@ -14267,7 +13471,7 @@
       <c r="I53" s="12"/>
       <c r="J53" s="12"/>
       <c r="K53" s="12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="L53" s="12"/>
       <c r="M53" s="12"/>
@@ -14347,7 +13551,7 @@
       <c r="I55" s="12"/>
       <c r="J55" s="12"/>
       <c r="K55" s="12" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L55" s="12"/>
       <c r="M55" s="12"/>
@@ -14388,7 +13592,7 @@
       <c r="I56" s="12"/>
       <c r="J56" s="12"/>
       <c r="K56" s="12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="L56" s="12"/>
       <c r="M56" s="12"/>
@@ -14468,7 +13672,7 @@
       <c r="I58" s="12"/>
       <c r="J58" s="12"/>
       <c r="K58" s="12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L58" s="12"/>
       <c r="M58" s="12"/>
@@ -14509,7 +13713,7 @@
       <c r="I59" s="12"/>
       <c r="J59" s="12"/>
       <c r="K59" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="L59" s="12"/>
       <c r="M59" s="12"/>
@@ -14588,7 +13792,7 @@
       <c r="H61" s="10"/>
       <c r="I61" s="12"/>
       <c r="J61" s="76" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="K61" s="76"/>
       <c r="L61" s="76"/>
@@ -14630,7 +13834,7 @@
       <c r="I62" s="12"/>
       <c r="J62" s="76"/>
       <c r="K62" s="76" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L62" s="76"/>
       <c r="M62" s="76"/>
@@ -14671,7 +13875,7 @@
       <c r="I63" s="12"/>
       <c r="J63" s="76"/>
       <c r="K63" s="76" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L63" s="76"/>
       <c r="M63" s="76"/>
@@ -14750,7 +13954,7 @@
       <c r="H65" s="10"/>
       <c r="I65" s="12"/>
       <c r="J65" s="89" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="K65" s="89"/>
       <c r="L65" s="89"/>
@@ -14774,7 +13978,7 @@
       <c r="AD65" s="12"/>
       <c r="AE65" s="44"/>
       <c r="AF65" s="90" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AG65" s="90"/>
       <c r="AH65" s="90"/>
@@ -15027,7 +14231,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:41">
       <c r="A1" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -15273,7 +14477,7 @@
     <row r="6" customHeight="1" spans="1:41">
       <c r="A6" s="10"/>
       <c r="B6" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
@@ -15375,7 +14579,7 @@
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
       <c r="R8" s="12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
@@ -15406,7 +14610,7 @@
       <c r="D9" s="12"/>
       <c r="E9" s="12"/>
       <c r="G9" s="12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -15567,7 +14771,7 @@
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
@@ -15651,7 +14855,7 @@
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
@@ -16024,7 +15228,7 @@
     <row r="24" customHeight="1" spans="1:41">
       <c r="A24" s="10"/>
       <c r="B24" s="11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
